--- a/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1974.6</v>
+        <v>28389.96</v>
       </c>
       <c r="C4" t="n">
-        <v>589176</v>
+        <v>5205816</v>
       </c>
       <c r="D4" t="n">
-        <v>462924</v>
+        <v>4090284</v>
       </c>
       <c r="E4" t="n">
-        <v>148500</v>
+        <v>1611900</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>6900</v>
+        <v>84180</v>
       </c>
       <c r="H4" t="n">
-        <v>240</v>
+        <v>7530</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21180</v>
+        <v>177720</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3623.85</v>
+        <v>24279.84</v>
       </c>
       <c r="C5" t="n">
-        <v>669816</v>
+        <v>4129776</v>
       </c>
       <c r="D5" t="n">
-        <v>526284</v>
+        <v>3244824</v>
       </c>
       <c r="E5" t="n">
-        <v>138600</v>
+        <v>1078200</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>8850</v>
+        <v>68400</v>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>5190</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20550</v>
+        <v>151350</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4049.46</v>
+        <v>22286.61</v>
       </c>
       <c r="C6" t="n">
-        <v>509040</v>
+        <v>3623256</v>
       </c>
       <c r="D6" t="n">
-        <v>399960</v>
+        <v>2846844</v>
       </c>
       <c r="E6" t="n">
-        <v>79200</v>
+        <v>765000</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>8190</v>
+        <v>62970</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7530</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22350</v>
+        <v>149160</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3184.11</v>
+        <v>31651.47</v>
       </c>
       <c r="C7" t="n">
-        <v>286272</v>
+        <v>4622688</v>
       </c>
       <c r="D7" t="n">
-        <v>224928</v>
+        <v>3632112</v>
       </c>
       <c r="E7" t="n">
-        <v>44100</v>
+        <v>946800</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>5460</v>
+        <v>83550</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>14760</v>
+        <v>193440</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1675.08</v>
+        <v>30235.23</v>
       </c>
       <c r="C8" t="n">
-        <v>97776</v>
+        <v>2904048</v>
       </c>
       <c r="D8" t="n">
-        <v>76824</v>
+        <v>2281752</v>
       </c>
       <c r="E8" t="n">
-        <v>20700</v>
+        <v>361800</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2370</v>
+        <v>70050</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5460</v>
+        <v>155040</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>788.58</v>
+        <v>24742.62</v>
       </c>
       <c r="C9" t="n">
-        <v>38808</v>
+        <v>1906632</v>
       </c>
       <c r="D9" t="n">
-        <v>30492</v>
+        <v>1498068</v>
       </c>
       <c r="E9" t="n">
-        <v>11700</v>
+        <v>157500</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1140</v>
+        <v>37230</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1050</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>449.73</v>
+        <v>17523.09</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1082088</v>
       </c>
       <c r="D10" t="n">
-        <v>9504</v>
+        <v>850212</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>64800</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>30750</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>46650</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.15</v>
+        <v>2909.07</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>208656</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>163944</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>4140</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>13080</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>164.34</v>
+        <v>434.16</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>55944</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>43956</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1470</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>129.06</v>
+        <v>183.6</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>13608</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>10692</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>141.66</v>
+        <v>145.62</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1584</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>15.66</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>16.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>12.42</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>6.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1630.73</v>
+        <v>10925.93</v>
       </c>
       <c r="C5" t="n">
-        <v>368398.8</v>
+        <v>2271376.8</v>
       </c>
       <c r="D5" t="n">
-        <v>174200</v>
+        <v>1074036.74</v>
       </c>
       <c r="E5" t="n">
-        <v>15287.58</v>
+        <v>118925.46</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4</v>
+        <v>1868.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4315.5</v>
+        <v>31783.5</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3239.57</v>
+        <v>17829.29</v>
       </c>
       <c r="C6" t="n">
-        <v>458136</v>
+        <v>3260930.4</v>
       </c>
       <c r="D6" t="n">
-        <v>202779.72</v>
+        <v>1443349.91</v>
       </c>
       <c r="E6" t="n">
-        <v>13384.8</v>
+        <v>129285</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>409.5</v>
+        <v>3148.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4292.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8269.5</v>
+        <v>55189.2</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3024.9</v>
+        <v>30068.9</v>
       </c>
       <c r="C7" t="n">
-        <v>286272</v>
+        <v>4622688</v>
       </c>
       <c r="D7" t="n">
-        <v>143504.06</v>
+        <v>2317287.46</v>
       </c>
       <c r="E7" t="n">
-        <v>9380.07</v>
+        <v>201384.36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>819</v>
+        <v>12532.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8979</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8856</v>
+        <v>116064</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1675.08</v>
+        <v>30235.23</v>
       </c>
       <c r="C8" t="n">
-        <v>97776</v>
+        <v>2904048</v>
       </c>
       <c r="D8" t="n">
-        <v>56542.46</v>
+        <v>1679369.47</v>
       </c>
       <c r="E8" t="n">
-        <v>5077.71</v>
+        <v>88749.53999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1540.5</v>
+        <v>45532.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3595.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3876.6</v>
+        <v>110078.4</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>788.58</v>
+        <v>24742.62</v>
       </c>
       <c r="C9" t="n">
-        <v>38808</v>
+        <v>1906632</v>
       </c>
       <c r="D9" t="n">
-        <v>24485.08</v>
+        <v>1202948.6</v>
       </c>
       <c r="E9" t="n">
-        <v>3132.09</v>
+        <v>42162.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>969</v>
+        <v>31645.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>850.5</v>
+        <v>72171</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>449.73</v>
+        <v>17523.09</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1082088</v>
       </c>
       <c r="D10" t="n">
-        <v>8268.48</v>
+        <v>739684.4399999999</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>18792</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>30750</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>41518.5</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.15</v>
+        <v>2909.07</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>208656</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>147303.68</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4057.02</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>4140</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>13080</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>164.34</v>
+        <v>434.16</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>55944</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>40747.21</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1290.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1470</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>129.06</v>
+        <v>183.6</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>13608</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>10152.05</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>141.66</v>
+        <v>145.62</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1539.65</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>15.66</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>16.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>12.42</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>6.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3587611.5</v>
+        <v>24037041.6</v>
       </c>
       <c r="C5" t="n">
-        <v>20261934</v>
+        <v>124925724</v>
       </c>
       <c r="D5" t="n">
-        <v>17651686.41</v>
+        <v>108832143.27</v>
       </c>
       <c r="E5" t="n">
-        <v>2816583.74</v>
+        <v>21910826.75</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>15833.46</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8963.459999999999</v>
+        <v>516892.86</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>139999.2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40652.01</v>
+        <v>299400.57</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7127049.6</v>
+        <v>39224433.6</v>
       </c>
       <c r="C6" t="n">
-        <v>25197480</v>
+        <v>179351172</v>
       </c>
       <c r="D6" t="n">
-        <v>20547669.03</v>
+        <v>146254646.18</v>
       </c>
       <c r="E6" t="n">
-        <v>2466015.55</v>
+        <v>23819468.4</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>70833.89999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>7575.75</v>
+        <v>58247.25</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1187409.46</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77898.69</v>
+        <v>519882.26</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6654789.9</v>
+        <v>66151572.3</v>
       </c>
       <c r="C7" t="n">
-        <v>15744960</v>
+        <v>254247840</v>
       </c>
       <c r="D7" t="n">
-        <v>14541266.81</v>
+        <v>234810737.92</v>
       </c>
       <c r="E7" t="n">
-        <v>1728184.1</v>
+        <v>37103054.49</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15151.5</v>
+        <v>231851.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2484040.35</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>83423.52</v>
+        <v>1093322.88</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3685176</v>
+        <v>66517506</v>
       </c>
       <c r="C8" t="n">
-        <v>5377680</v>
+        <v>159722640</v>
       </c>
       <c r="D8" t="n">
-        <v>5729447.88</v>
+        <v>170170508.6</v>
       </c>
       <c r="E8" t="n">
-        <v>935517.29</v>
+        <v>16351215.25</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>28499.25</v>
+        <v>842351.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>994695.08</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>36517.57</v>
+        <v>1036938.53</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1734876</v>
+        <v>54433764</v>
       </c>
       <c r="C9" t="n">
-        <v>2134440</v>
+        <v>104864760</v>
       </c>
       <c r="D9" t="n">
-        <v>2481072.75</v>
+        <v>121894782.04</v>
       </c>
       <c r="E9" t="n">
-        <v>577056.26</v>
+        <v>7768065.06</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>17926.5</v>
+        <v>585441.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>141091.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8011.71</v>
+        <v>679850.8199999999</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>989406</v>
+        <v>38550798</v>
       </c>
       <c r="C10" t="n">
-        <v>665280</v>
+        <v>59514840</v>
       </c>
       <c r="D10" t="n">
-        <v>837845.08</v>
+        <v>74952224.31</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>3462238.08</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12765</v>
+        <v>568875</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5784.82</v>
+        <v>391104.27</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>640530</v>
+        <v>6399954</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>11476080</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>14926282.3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>747465.36</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>76590</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>123213.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>361548</v>
+        <v>955152</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>3076920</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>4128914.99</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>237780.14</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>27195</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>56802.6</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>283932</v>
+        <v>403920</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>748440</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>1028707.63</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6660</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>29390.4</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>311652</v>
+        <v>320364</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>156012.53</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>3885</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>12151.8</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>14058</v>
+        <v>34452</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4804.2</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>3564</v>
+        <v>35244</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>27324</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>13464</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4804.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>5148</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>68265</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28389.96</v>
+        <v>38541.24</v>
       </c>
       <c r="C4" t="n">
-        <v>5205816</v>
+        <v>4055688</v>
       </c>
       <c r="D4" t="n">
-        <v>4090284</v>
+        <v>3186612</v>
       </c>
       <c r="E4" t="n">
-        <v>1611900</v>
+        <v>1124100</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>84180</v>
+        <v>117210</v>
       </c>
       <c r="H4" t="n">
-        <v>7530</v>
+        <v>14850</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>177720</v>
+        <v>372030</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24279.84</v>
+        <v>13576.95</v>
       </c>
       <c r="C5" t="n">
-        <v>4129776</v>
+        <v>884016</v>
       </c>
       <c r="D5" t="n">
-        <v>3244824</v>
+        <v>694584</v>
       </c>
       <c r="E5" t="n">
-        <v>1078200</v>
+        <v>257400</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>68400</v>
+        <v>35100</v>
       </c>
       <c r="H5" t="n">
-        <v>5190</v>
+        <v>3180</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>151350</v>
+        <v>124680</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>22286.61</v>
+        <v>1346.94</v>
       </c>
       <c r="C6" t="n">
-        <v>3623256</v>
+        <v>117432</v>
       </c>
       <c r="D6" t="n">
-        <v>2846844</v>
+        <v>92268</v>
       </c>
       <c r="E6" t="n">
-        <v>765000</v>
+        <v>34200</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>62970</v>
+        <v>4920</v>
       </c>
       <c r="H6" t="n">
-        <v>7530</v>
+        <v>390</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>149160</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31651.47</v>
+        <v>173.79</v>
       </c>
       <c r="C7" t="n">
-        <v>4622688</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>3632112</v>
+        <v>23760</v>
       </c>
       <c r="E7" t="n">
-        <v>946800</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83550</v>
+        <v>1050</v>
       </c>
       <c r="H7" t="n">
-        <v>12300</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>193440</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30235.23</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2904048</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>2281752</v>
+        <v>1188</v>
       </c>
       <c r="E8" t="n">
-        <v>361800</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>70050</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>4230</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>155040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24742.62</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1906632</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1498068</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>157500</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>37230</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>89100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17523.09</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1082088</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>850212</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>64800</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30750</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>46650</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>2909.07</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>208656</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>163944</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4140</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13080</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>434.16</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55944</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>43956</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>183.6</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>10692</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>145.62</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>15.66</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>16.02</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>12.42</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10925.93</v>
+        <v>6109.63</v>
       </c>
       <c r="C5" t="n">
-        <v>2271376.8</v>
+        <v>486208.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1074036.74</v>
+        <v>229907.3</v>
       </c>
       <c r="E5" t="n">
-        <v>118925.46</v>
+        <v>28391.22</v>
       </c>
       <c r="F5" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1868.4</v>
+        <v>1144.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31783.5</v>
+        <v>26182.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>17829.29</v>
+        <v>1077.55</v>
       </c>
       <c r="C6" t="n">
-        <v>3260930.4</v>
+        <v>105688.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1443349.91</v>
+        <v>46779.88</v>
       </c>
       <c r="E6" t="n">
-        <v>129285</v>
+        <v>5779.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3148.5</v>
+        <v>246</v>
       </c>
       <c r="H6" t="n">
-        <v>4292.1</v>
+        <v>222.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>55189.2</v>
+        <v>7969.8</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>30068.9</v>
+        <v>165.1</v>
       </c>
       <c r="C7" t="n">
-        <v>4622688</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>2317287.46</v>
+        <v>15158.88</v>
       </c>
       <c r="E7" t="n">
-        <v>201384.36</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12532.5</v>
+        <v>157.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8979</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>116064</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30235.23</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2904048</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>1679369.47</v>
+        <v>874.37</v>
       </c>
       <c r="E8" t="n">
-        <v>88749.53999999999</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>45532.5</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3595.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>110078.4</v>
+        <v>511.2</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24742.62</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1906632</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1202948.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>42162.75</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>31645.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>72171</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17523.09</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1082088</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>739684.4399999999</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>18792</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30750</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>41518.5</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>2909.07</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>208656</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>147303.68</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4057.02</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4140</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13080</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>434.16</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55944</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>40747.21</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1290.6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>183.6</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>10152.05</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>145.62</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1539.65</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>15.66</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>16.02</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>12.42</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24037041.6</v>
+        <v>13441180.5</v>
       </c>
       <c r="C5" t="n">
-        <v>124925724</v>
+        <v>26741484</v>
       </c>
       <c r="D5" t="n">
-        <v>108832143.27</v>
+        <v>23296507.11</v>
       </c>
       <c r="E5" t="n">
-        <v>21910826.75</v>
+        <v>5230798.37</v>
       </c>
       <c r="F5" t="n">
-        <v>15833.46</v>
+        <v>10000.08</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>516892.86</v>
+        <v>316708.92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>139999.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>299400.57</v>
+        <v>246641.98</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>39224433.6</v>
+        <v>2370614.4</v>
       </c>
       <c r="C6" t="n">
-        <v>179351172</v>
+        <v>5812884</v>
       </c>
       <c r="D6" t="n">
-        <v>146254646.18</v>
+        <v>4740204.84</v>
       </c>
       <c r="E6" t="n">
-        <v>23819468.4</v>
+        <v>1064870.35</v>
       </c>
       <c r="F6" t="n">
-        <v>70833.89999999999</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>58247.25</v>
+        <v>4551</v>
       </c>
       <c r="H6" t="n">
-        <v>1187409.46</v>
+        <v>61499.29</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>519882.26</v>
+        <v>75075.52</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>66151572.3</v>
+        <v>363221.1</v>
       </c>
       <c r="C7" t="n">
-        <v>254247840</v>
+        <v>1663200</v>
       </c>
       <c r="D7" t="n">
-        <v>234810737.92</v>
+        <v>1536049.31</v>
       </c>
       <c r="E7" t="n">
-        <v>37103054.49</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>231851.25</v>
+        <v>2913.75</v>
       </c>
       <c r="H7" t="n">
-        <v>2484040.35</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1093322.88</v>
+        <v>19329.84</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>66517506</v>
+        <v>34254</v>
       </c>
       <c r="C8" t="n">
-        <v>159722640</v>
+        <v>83160</v>
       </c>
       <c r="D8" t="n">
-        <v>170170508.6</v>
+        <v>88599.71000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>16351215.25</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
-        <v>79167.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>842351.25</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>994695.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1036938.53</v>
+        <v>4815.5</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>54433764</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>104864760</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>121894782.04</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7768065.06</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>585441.75</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>141091.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>679850.8199999999</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>38550798</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>59514840</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>74952224.31</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3462238.08</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>568875</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>391104.27</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>6399954</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11476080</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>14926282.3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>747465.36</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>76590</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>123213.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>955152</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3076920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4128914.99</v>
-      </c>
-      <c r="E12" t="n">
-        <v>237780.14</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>27195</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>56802.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>403920</v>
-      </c>
-      <c r="C13" t="n">
-        <v>748440</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1028707.63</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>29390.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>320364</v>
-      </c>
-      <c r="C14" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D14" t="n">
-        <v>156012.53</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12151.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>34452</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>35244</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27324</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>555</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>13464</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>5148</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5652</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>594</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>68265</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3696.48</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1091664</v>
-      </c>
-      <c r="D4" t="n">
-        <v>857736</v>
-      </c>
-      <c r="E4" t="n">
-        <v>384300</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13260</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3990</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>33330</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4610.43</v>
-      </c>
-      <c r="C5" t="n">
-        <v>975240</v>
-      </c>
-      <c r="D5" t="n">
-        <v>766260</v>
-      </c>
-      <c r="E5" t="n">
-        <v>228600</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16050</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2910</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>34800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4486.32</v>
-      </c>
-      <c r="C6" t="n">
-        <v>590688</v>
-      </c>
-      <c r="D6" t="n">
-        <v>464112</v>
-      </c>
-      <c r="E6" t="n">
-        <v>122400</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12990</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>25710</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3833.19</v>
-      </c>
-      <c r="C7" t="n">
-        <v>338688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>266112</v>
-      </c>
-      <c r="E7" t="n">
-        <v>68400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H7" t="n">
-        <v>510</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14820</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4236.84</v>
-      </c>
-      <c r="C8" t="n">
-        <v>272160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>213840</v>
-      </c>
-      <c r="E8" t="n">
-        <v>37800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11490</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4123.98</v>
-      </c>
-      <c r="C9" t="n">
-        <v>197064</v>
-      </c>
-      <c r="D9" t="n">
-        <v>154836</v>
-      </c>
-      <c r="E9" t="n">
-        <v>30600</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3900</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10410</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3114.99</v>
-      </c>
-      <c r="C10" t="n">
-        <v>123984</v>
-      </c>
-      <c r="D10" t="n">
-        <v>97416</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3540</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8220</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2168.46</v>
-      </c>
-      <c r="C11" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36828</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>780</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1220.58</v>
-      </c>
-      <c r="C12" t="n">
-        <v>13608</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10692</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>717.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>452.07</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>352.98</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>311.85</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>404.82</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>172.35</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2074.69</v>
-      </c>
-      <c r="C5" t="n">
-        <v>536382</v>
-      </c>
-      <c r="D5" t="n">
-        <v>253632.06</v>
-      </c>
-      <c r="E5" t="n">
-        <v>25214.58</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1047.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7308</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3589.06</v>
-      </c>
-      <c r="C6" t="n">
-        <v>531619.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>235304.78</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20685.6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>649.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>615.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9512.700000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3641.53</v>
-      </c>
-      <c r="C7" t="n">
-        <v>338688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>169779.46</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14548.68</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>747</v>
-      </c>
-      <c r="H7" t="n">
-        <v>372.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4236.84</v>
-      </c>
-      <c r="C8" t="n">
-        <v>272160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>157386.24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9272.34</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2125.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8157.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4123.98</v>
-      </c>
-      <c r="C9" t="n">
-        <v>197064</v>
-      </c>
-      <c r="D9" t="n">
-        <v>124333.31</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8191.62</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3315</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8432.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3114.99</v>
-      </c>
-      <c r="C10" t="n">
-        <v>123984</v>
-      </c>
-      <c r="D10" t="n">
-        <v>84751.92</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3132</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3540</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7315.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2168.46</v>
-      </c>
-      <c r="C11" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33089.96</v>
-      </c>
-      <c r="E11" t="n">
-        <v>737.64</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>780</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1220.58</v>
-      </c>
-      <c r="C12" t="n">
-        <v>13608</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9911.48</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>717.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2632.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>452.07</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3079.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>352.98</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>311.85</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>404.82</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>172.35</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4564325.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>29501010</v>
-      </c>
-      <c r="D5" t="n">
-        <v>25700536.64</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4645534.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>289818.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68841.36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7895923.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29239056</v>
-      </c>
-      <c r="D6" t="n">
-        <v>23843433.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3811114.94</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12015.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>170305.74</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>89609.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8011367.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18627840</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17203752.28</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2680448.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13819.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>102996.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>83762.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9321048</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14968800</v>
-      </c>
-      <c r="D8" t="n">
-        <v>15947947.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1708335.92</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39321.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76847.42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>9072756</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10838520</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12598694.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1509224.07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>61327.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>79430.38</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6852978</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6819120</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8587912.050000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>577039.6800000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>65490</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>68914.84</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4770612</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2577960</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3353005.44</v>
-      </c>
-      <c r="E11" t="n">
-        <v>135902.79</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14430</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>18651.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2685276</v>
-      </c>
-      <c r="C12" t="n">
-        <v>748440</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1004330.67</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1578060</v>
-      </c>
-      <c r="C13" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D13" t="n">
-        <v>266701.98</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>994554</v>
-      </c>
-      <c r="C14" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D14" t="n">
-        <v>312025.06</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>776556</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>686070</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>890604</v>
-      </c>
-      <c r="C17" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D17" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>379170</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>85536</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>44748</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>38541.24</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4055688</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3186612</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1124100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>117210</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14850</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>372030</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13576.95</v>
-      </c>
-      <c r="C5" t="n">
-        <v>884016</v>
-      </c>
-      <c r="D5" t="n">
-        <v>694584</v>
-      </c>
-      <c r="E5" t="n">
-        <v>257400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>35100</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3180</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124680</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1346.94</v>
-      </c>
-      <c r="C6" t="n">
-        <v>117432</v>
-      </c>
-      <c r="D6" t="n">
-        <v>92268</v>
-      </c>
-      <c r="E6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4920</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21540</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>173.79</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>23760</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6109.63</v>
-      </c>
-      <c r="C5" t="n">
-        <v>486208.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>229907.3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>28391.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1144.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26182.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1077.55</v>
-      </c>
-      <c r="C6" t="n">
-        <v>105688.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46779.88</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5779.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>246</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7969.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>165.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15158.88</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>874.37</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>511.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13441180.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>26741484</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23296507.11</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5230798.37</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10000.08</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>316708.92</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>246641.98</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2370614.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5812884</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4740204.84</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1064870.35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75075.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>363221.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1663200</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1536049.31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2913.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>19329.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>34254</v>
-      </c>
-      <c r="C8" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88599.71000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4815.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
@@ -538,7 +538,7 @@
         <v>64230</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -576,7 +576,7 @@
         <v>54720</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -614,7 +614,7 @@
         <v>42870</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
@@ -652,7 +652,7 @@
         <v>47670</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -690,7 +690,7 @@
         <v>30600</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>12</v>
@@ -728,7 +728,7 @@
         <v>12180</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -766,7 +766,7 @@
         <v>3870</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -804,7 +804,7 @@
         <v>4230</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -842,7 +842,7 @@
         <v>5700</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -918,7 +918,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>2940</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>3690</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>5640</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>2940</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -2668,7 +2668,7 @@
         <v>3690</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         <v>5640</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>813351</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>291665</v>
@@ -3600,7 +3600,7 @@
         <v>1020838.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3638,7 +3638,7 @@
         <v>1560306</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7530</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>5190</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -9934,7 +9934,7 @@
         <v>7530</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>12300</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>4230</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19699.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J5" t="n">
         <v>6.6</v>
@@ -10866,7 +10866,7 @@
         <v>24435.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
@@ -10904,7 +10904,7 @@
         <v>34799.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -10942,7 +10942,7 @@
         <v>26010</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>10.2</v>
@@ -10980,7 +10980,7 @@
         <v>12180</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>5.7</v>
@@ -11018,7 +11018,7 @@
         <v>3870</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -11056,7 +11056,7 @@
         <v>4230</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -11094,7 +11094,7 @@
         <v>5700</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -11170,7 +11170,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1868.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -11798,7 +11798,7 @@
         <v>4292.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>8979</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11874,7 +11874,7 @@
         <v>3595.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>516892.86</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>
@@ -12730,7 +12730,7 @@
         <v>1187409.46</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2484040.35</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12806,7 +12806,7 @@
         <v>994695.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>14850</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -16420,7 +16420,7 @@
         <v>5449783.68</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>402496.5</v>
       </c>
       <c r="J5" t="n">
         <v>384997.8</v>
@@ -16458,7 +16458,7 @@
         <v>6760191.73</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>437497.5</v>
@@ -16496,7 +16496,7 @@
         <v>9627171.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -16534,7 +16534,7 @@
         <v>7195666.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>594996.6</v>
@@ -16572,7 +16572,7 @@
         <v>3369597</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>332498.1</v>
@@ -16610,7 +16610,7 @@
         <v>1070635.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>524997</v>
@@ -16648,7 +16648,7 @@
         <v>1170229.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>291665</v>
@@ -16686,7 +16686,7 @@
         <v>1576905</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>116666</v>
@@ -16762,7 +16762,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>2910</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -17352,7 +17352,7 @@
         <v>6480</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -17504,7 +17504,7 @@
         <v>7140</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -18284,7 +18284,7 @@
         <v>2332.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
@@ -18436,7 +18436,7 @@
         <v>7140</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>2.85</v>
@@ -19216,7 +19216,7 @@
         <v>645369.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>34999.8</v>
@@ -19368,7 +19368,7 @@
         <v>1975281</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>166249.05</v>
@@ -20110,7 +20110,7 @@
         <v>16080</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>12</v>
@@ -20148,7 +20148,7 @@
         <v>22860</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -21080,7 +21080,7 @@
         <v>8229.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -22012,7 +22012,7 @@
         <v>2276718.84</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
@@ -544,7 +544,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="L4" t="n">
         <v>1469040</v>
@@ -582,7 +582,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
         <v>921720</v>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="L6" t="n">
         <v>579690</v>
@@ -658,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
         <v>542160</v>
@@ -696,7 +696,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="L8" t="n">
         <v>469020</v>
@@ -734,7 +734,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
         <v>394920</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="L10" t="n">
         <v>322710</v>
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L11" t="n">
         <v>202740</v>
@@ -848,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L12" t="n">
         <v>153990</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L13" t="n">
         <v>120420</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>49170</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>23820</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>9840</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3150</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>17010</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>20280</v>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
         <v>20100</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
         <v>24810</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>35400</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>41790</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>45750</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>49170</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>83490</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>85200</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
         <v>38460</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>18450</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8460</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>4258.8</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="L6" t="n">
         <v>7437</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="L7" t="n">
         <v>14886</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="L8" t="n">
         <v>25134</v>
@@ -2598,7 +2598,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>33849.9</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>40717.5</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>49170</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>83490</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>85200</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
         <v>38460</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>18450</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8460</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>40117.9</v>
@@ -3416,7 +3416,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>249607.8</v>
       </c>
       <c r="L6" t="n">
         <v>70056.53999999999</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>349877.6</v>
       </c>
       <c r="L7" t="n">
         <v>140226.12</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>307209.6</v>
       </c>
       <c r="L8" t="n">
         <v>236762.28</v>
@@ -3530,7 +3530,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L9" t="n">
         <v>318866.06</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L10" t="n">
         <v>383558.85</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L11" t="n">
         <v>463181.4</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>746690</v>
       </c>
       <c r="L12" t="n">
         <v>786475.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>853360</v>
       </c>
       <c r="L13" t="n">
         <v>802584</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L14" t="n">
         <v>362293.2</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L15" t="n">
         <v>173799</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L16" t="n">
         <v>79693.2</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>23455.8</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>153330</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>62340</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>12750</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3270</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="L5" t="n">
         <v>13091.4</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>4717.5</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1962</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>277768.68</v>
       </c>
       <c r="L5" t="n">
         <v>123320.99</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>44438.85</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>18482.04</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L4" t="n">
         <v>150360</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
         <v>53640</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
         <v>16590</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>4620</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23.94</v>
       </c>
       <c r="L5" t="n">
         <v>11264.4</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
         <v>6138.3</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>2772</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>510735.96</v>
       </c>
       <c r="L5" t="n">
         <v>106110.65</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>138671</v>
       </c>
       <c r="L6" t="n">
         <v>57822.79</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>26112.24</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>16854.26</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="L4" t="n">
         <v>177720</v>
@@ -9902,7 +9902,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L5" t="n">
         <v>151350</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="L6" t="n">
         <v>149160</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="L7" t="n">
         <v>193440</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L8" t="n">
         <v>155040</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>89100</v>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
         <v>46650</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>13080</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6030</v>
@@ -10834,7 +10834,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>274.26</v>
       </c>
       <c r="L5" t="n">
         <v>193561.2</v>
@@ -10872,7 +10872,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>267.8</v>
       </c>
       <c r="L6" t="n">
         <v>214485.3</v>
@@ -10910,7 +10910,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>376.38</v>
       </c>
       <c r="L7" t="n">
         <v>325296</v>
@@ -10948,7 +10948,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>347.4</v>
       </c>
       <c r="L8" t="n">
         <v>333004.2</v>
@@ -10986,7 +10986,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
         <v>319885.2</v>
@@ -11024,7 +11024,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="L10" t="n">
         <v>287211.9</v>
@@ -11062,7 +11062,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L11" t="n">
         <v>202740</v>
@@ -11100,7 +11100,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L12" t="n">
         <v>153990</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L13" t="n">
         <v>120420</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>49170</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>23820</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>9840</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3150</v>
@@ -11766,7 +11766,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.14</v>
       </c>
       <c r="L5" t="n">
         <v>31783.5</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>55189.2</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>163.18</v>
       </c>
       <c r="L7" t="n">
         <v>116064</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>139.5</v>
       </c>
       <c r="L8" t="n">
         <v>110078.4</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>72171</v>
@@ -11956,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
         <v>41518.5</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>13080</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6030</v>
@@ -12698,7 +12698,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1496366.76</v>
       </c>
       <c r="L5" t="n">
         <v>299400.57</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1858191.4</v>
       </c>
       <c r="L6" t="n">
         <v>519882.26</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3481282.12</v>
       </c>
       <c r="L7" t="n">
         <v>1093322.88</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2976093</v>
       </c>
       <c r="L8" t="n">
         <v>1036938.53</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2112066</v>
       </c>
       <c r="L9" t="n">
         <v>679850.8199999999</v>
@@ -12888,7 +12888,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1237372</v>
       </c>
       <c r="L10" t="n">
         <v>391104.27</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L11" t="n">
         <v>123213.6</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L12" t="n">
         <v>56802.6</v>
@@ -13592,7 +13592,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
         <v>372030</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>124680</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>21540</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="n">
         <v>26182.8</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>7969.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>304649.52</v>
       </c>
       <c r="L5" t="n">
         <v>246641.98</v>
@@ -15532,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>75075.52</v>
@@ -16426,7 +16426,7 @@
         <v>384997.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5851062.84</v>
       </c>
       <c r="L5" t="n">
         <v>1823346.5</v>
@@ -16464,7 +16464,7 @@
         <v>437497.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5713245.2</v>
       </c>
       <c r="L6" t="n">
         <v>2020451.53</v>
@@ -16502,7 +16502,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8029690.92</v>
       </c>
       <c r="L7" t="n">
         <v>3064288.32</v>
@@ -16540,7 +16540,7 @@
         <v>594996.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7411431.6</v>
       </c>
       <c r="L8" t="n">
         <v>3136899.56</v>
@@ -16578,7 +16578,7 @@
         <v>332498.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7317562</v>
       </c>
       <c r="L9" t="n">
         <v>3013318.58</v>
@@ -16616,7 +16616,7 @@
         <v>524997</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6250862</v>
       </c>
       <c r="L10" t="n">
         <v>2705536.1</v>
@@ -16654,7 +16654,7 @@
         <v>291665</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4053460</v>
       </c>
       <c r="L11" t="n">
         <v>1909810.8</v>
@@ -16692,7 +16692,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2453410</v>
       </c>
       <c r="L12" t="n">
         <v>1450585.8</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1493380</v>
       </c>
       <c r="L13" t="n">
         <v>1134356.4</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L14" t="n">
         <v>463181.4</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>298676</v>
       </c>
       <c r="L15" t="n">
         <v>224384.4</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>92692.8</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L17" t="n">
         <v>29673</v>
@@ -17320,7 +17320,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L4" t="n">
         <v>134460</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
         <v>164370</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L6" t="n">
         <v>162210</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L7" t="n">
         <v>179970</v>
@@ -17472,7 +17472,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L8" t="n">
         <v>219390</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
         <v>245970</v>
@@ -17548,7 +17548,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
         <v>219570</v>
@@ -17586,7 +17586,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L11" t="n">
         <v>137490</v>
@@ -17624,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
         <v>63420</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L13" t="n">
         <v>31950</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>8880</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4860</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1080</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>61.74</v>
       </c>
       <c r="L5" t="n">
         <v>34517.7</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>86.45</v>
       </c>
       <c r="L6" t="n">
         <v>60017.7</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>123.82</v>
       </c>
       <c r="L7" t="n">
         <v>107982</v>
@@ -18404,7 +18404,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>169.2</v>
       </c>
       <c r="L8" t="n">
         <v>155766.9</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
         <v>199235.7</v>
@@ -18480,7 +18480,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
         <v>195417.3</v>
@@ -18518,7 +18518,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L11" t="n">
         <v>137490</v>
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
         <v>63420</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L13" t="n">
         <v>31950</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>8880</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4860</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1080</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1317161.16</v>
       </c>
       <c r="L5" t="n">
         <v>325156.73</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1844324.3</v>
       </c>
       <c r="L6" t="n">
         <v>565366.73</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2641575.88</v>
       </c>
       <c r="L7" t="n">
         <v>1017190.44</v>
@@ -19336,7 +19336,7 @@
         <v>545413.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3609712.8</v>
       </c>
       <c r="L8" t="n">
         <v>1467324.2</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4608144</v>
       </c>
       <c r="L9" t="n">
         <v>1876800.29</v>
@@ -19412,7 +19412,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4501474</v>
       </c>
       <c r="L10" t="n">
         <v>1840830.97</v>
@@ -19450,7 +19450,7 @@
         <v>233332</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3264102</v>
       </c>
       <c r="L11" t="n">
         <v>1295155.8</v>
@@ -19488,7 +19488,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1642718</v>
       </c>
       <c r="L12" t="n">
         <v>597416.4</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>618686</v>
       </c>
       <c r="L13" t="n">
         <v>300969</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L14" t="n">
         <v>83649.60000000001</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>45781.2</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>10173.6</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>3673.8</v>
@@ -20116,7 +20116,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>406950</v>
@@ -20154,7 +20154,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="L5" t="n">
         <v>285480</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="L6" t="n">
         <v>142200</v>
@@ -20230,7 +20230,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
         <v>94830</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
         <v>36720</v>
@@ -20306,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>5880</v>
@@ -21086,7 +21086,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>87.78</v>
       </c>
       <c r="L5" t="n">
         <v>59950.8</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
       <c r="L6" t="n">
         <v>52614</v>
@@ -21162,7 +21162,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>68.88</v>
       </c>
       <c r="L7" t="n">
         <v>56898</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="L8" t="n">
         <v>26071.2</v>
@@ -21238,7 +21238,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>4762.8</v>
@@ -22018,7 +22018,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1872698.52</v>
       </c>
       <c r="L5" t="n">
         <v>564736.54</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1553115.2</v>
       </c>
       <c r="L6" t="n">
         <v>495623.88</v>
@@ -22094,7 +22094,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1469485.92</v>
       </c>
       <c r="L7" t="n">
         <v>535979.16</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>460814.4</v>
       </c>
       <c r="L8" t="n">
         <v>245590.7</v>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>44865.58</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
@@ -549,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>1159</v>
+        <v>450</v>
       </c>
       <c r="L4" t="n">
         <v>1465800</v>
@@ -590,7 +590,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>636</v>
+        <v>267</v>
       </c>
       <c r="L5" t="n">
         <v>919860</v>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>154</v>
       </c>
       <c r="L6" t="n">
         <v>577860</v>
@@ -672,7 +672,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>175</v>
       </c>
       <c r="L7" t="n">
         <v>541110</v>
@@ -713,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>386</v>
+        <v>109</v>
       </c>
       <c r="L8" t="n">
         <v>468300</v>
@@ -754,7 +754,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>343</v>
+        <v>107</v>
       </c>
       <c r="L9" t="n">
         <v>394560</v>
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>293</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
         <v>322620</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="L11" t="n">
         <v>202470</v>
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
         <v>153780</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
         <v>120420</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>49170</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>23820</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>9840</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3150</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>17010</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>20250</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>20130</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>24900</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>35580</v>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>42000</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>45780</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>49320</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>83700</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>85230</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>38520</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18510</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8460</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
         <v>4252.5</v>
@@ -2639,7 +2639,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9.130000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>7448.1</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.76</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
         <v>14940</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
         <v>25261.8</v>
@@ -2762,7 +2762,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>18.47</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>34020</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>20.01</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>40744.2</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>23.36</v>
+        <v>2.7</v>
       </c>
       <c r="L11" t="n">
         <v>49320</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>32.44</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>83700</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>37.98</v>
+        <v>6.65</v>
       </c>
       <c r="L13" t="n">
         <v>85230</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.3</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>38520</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>11.83</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18510</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8460</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>112504.25</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
         <v>765450</v>
@@ -3643,7 +3643,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>443122.06</v>
+        <v>172325.24</v>
       </c>
       <c r="L6" t="n">
         <v>1340658</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>619574.5600000001</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
         <v>2689200</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>571795.46</v>
+        <v>321634.94</v>
       </c>
       <c r="L8" t="n">
         <v>4547124</v>
@@ -3766,7 +3766,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>896780.76</v>
+        <v>467885.62</v>
       </c>
       <c r="L9" t="n">
         <v>6123600</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>971605.5600000001</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>7333956</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1134316.72</v>
+        <v>130882.7</v>
       </c>
       <c r="L11" t="n">
         <v>8877600</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1575399.42</v>
+        <v>225057.06</v>
       </c>
       <c r="L12" t="n">
         <v>15066000</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1844156.88</v>
+        <v>322727.45</v>
       </c>
       <c r="L13" t="n">
         <v>15341400</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1179910.8</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>6933600</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>574514.59</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3331800</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1522800</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>448200</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
         <v>153240</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>63030</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>12690</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.26</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
         <v>13236.3</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4695.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>498233.12</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
         <v>2382534</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>845154</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>150450</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>54210</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>16860</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4590</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>18.87</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>11384.1</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>6238.2</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2754</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>916106.05</v>
+        <v>208936.47</v>
       </c>
       <c r="L5" t="n">
         <v>2049138</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>246178.92</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1122876</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>495720</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>322056</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="L4" t="n">
         <v>178200</v>
@@ -10630,7 +10630,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="L5" t="n">
         <v>151410</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="L6" t="n">
         <v>149250</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
         <v>193470</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
         <v>155130</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>89160</v>
@@ -10835,7 +10835,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
         <v>46650</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>13080</v>
@@ -11634,7 +11634,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>210.52</v>
+        <v>88.38</v>
       </c>
       <c r="L5" t="n">
         <v>193170.6</v>
@@ -11675,7 +11675,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>204.83</v>
+        <v>78.08</v>
       </c>
       <c r="L6" t="n">
         <v>213808.2</v>
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>292.2</v>
+        <v>111.65</v>
       </c>
       <c r="L7" t="n">
         <v>324666</v>
@@ -11757,7 +11757,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>284.1</v>
+        <v>80.22</v>
       </c>
       <c r="L8" t="n">
         <v>332493</v>
@@ -11798,7 +11798,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>275.43</v>
+        <v>85.92</v>
       </c>
       <c r="L9" t="n">
         <v>319593.6</v>
@@ -11839,7 +11839,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>254.91</v>
+        <v>65.25</v>
       </c>
       <c r="L10" t="n">
         <v>287131.8</v>
@@ -11880,7 +11880,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>170.72</v>
+        <v>37.74</v>
       </c>
       <c r="L11" t="n">
         <v>202470</v>
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>106.6</v>
+        <v>16.69</v>
       </c>
       <c r="L12" t="n">
         <v>153780</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>66.45999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
         <v>120420</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>33.05</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>49170</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>23820</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>9840</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3150</v>
@@ -12638,7 +12638,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>55.28</v>
+        <v>31.44</v>
       </c>
       <c r="L5" t="n">
         <v>31796.1</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>67.94</v>
+        <v>31.94</v>
       </c>
       <c r="L6" t="n">
         <v>55222.5</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>126.96</v>
+        <v>53.59</v>
       </c>
       <c r="L7" t="n">
         <v>116082</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>114.08</v>
+        <v>36.06</v>
       </c>
       <c r="L8" t="n">
         <v>110142.3</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>79.5</v>
+        <v>27.3</v>
       </c>
       <c r="L9" t="n">
         <v>72219.60000000001</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>51.33</v>
+        <v>13.05</v>
       </c>
       <c r="L10" t="n">
         <v>41518.5</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>9.880000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>13080</v>
@@ -13642,7 +13642,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2684030.01</v>
+        <v>1526843.42</v>
       </c>
       <c r="L5" t="n">
         <v>5723298</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3298797.53</v>
+        <v>1550927.2</v>
       </c>
       <c r="L6" t="n">
         <v>9940050</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6164766.87</v>
+        <v>2602213.15</v>
       </c>
       <c r="L7" t="n">
         <v>20894760</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5539268.48</v>
+        <v>1751123.58</v>
       </c>
       <c r="L8" t="n">
         <v>19825614</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3860056.33</v>
+        <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
         <v>12999528</v>
@@ -13847,7 +13847,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2492379.48</v>
+        <v>633655.8</v>
       </c>
       <c r="L10" t="n">
         <v>7473330</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>479903.23</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>2354400</v>
@@ -14605,7 +14605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
         <v>374610</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>125790</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>21270</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.25</v>
+        <v>5.63</v>
       </c>
       <c r="L5" t="n">
         <v>26415.9</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7869.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>546449.22</v>
+        <v>273224.61</v>
       </c>
       <c r="L5" t="n">
         <v>4754862</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1416582</v>
@@ -17658,7 +17658,7 @@
         <v>160234.8</v>
       </c>
       <c r="K5" t="n">
-        <v>10221814.9</v>
+        <v>4291233.61</v>
       </c>
       <c r="L5" t="n">
         <v>34770708</v>
@@ -17699,7 +17699,7 @@
         <v>182085</v>
       </c>
       <c r="K6" t="n">
-        <v>9945628.369999999</v>
+        <v>3791155.37</v>
       </c>
       <c r="L6" t="n">
         <v>38485476</v>
@@ -17740,7 +17740,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>14188257.42</v>
+        <v>5421277.4</v>
       </c>
       <c r="L7" t="n">
         <v>58439880</v>
@@ -17781,7 +17781,7 @@
         <v>247635.6</v>
       </c>
       <c r="K8" t="n">
-        <v>13794565.38</v>
+        <v>3895356.54</v>
       </c>
       <c r="L8" t="n">
         <v>59848740</v>
@@ -17822,7 +17822,7 @@
         <v>138384.6</v>
       </c>
       <c r="K9" t="n">
-        <v>13373730.52</v>
+        <v>4171980.08</v>
       </c>
       <c r="L9" t="n">
         <v>57526848</v>
@@ -17863,7 +17863,7 @@
         <v>218502</v>
       </c>
       <c r="K10" t="n">
-        <v>12377409.96</v>
+        <v>3168279</v>
       </c>
       <c r="L10" t="n">
         <v>51683724</v>
@@ -17904,7 +17904,7 @@
         <v>121390</v>
       </c>
       <c r="K11" t="n">
-        <v>8289237.54</v>
+        <v>1832357.77</v>
       </c>
       <c r="L11" t="n">
         <v>36444600</v>
@@ -17945,7 +17945,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>5176312.38</v>
+        <v>810205.42</v>
       </c>
       <c r="L12" t="n">
         <v>27680400</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>3227274.54</v>
+        <v>368831.38</v>
       </c>
       <c r="L13" t="n">
         <v>21675600</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1604678.69</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>8850600</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>670267.02</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4287600</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1771200</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>567000</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>131460</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>162870</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="L6" t="n">
         <v>161520</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="L7" t="n">
         <v>179130</v>
@@ -18785,7 +18785,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>218790</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
         <v>245610</v>
@@ -18867,7 +18867,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
         <v>219540</v>
@@ -18908,7 +18908,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
         <v>137340</v>
@@ -18949,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>63210</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>32010</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8910</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4860</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1080</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>43.36</v>
+        <v>22.18</v>
       </c>
       <c r="L5" t="n">
         <v>34202.7</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>63.38</v>
+        <v>24.34</v>
       </c>
       <c r="L6" t="n">
         <v>59762.4</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>95.7</v>
+        <v>40.19</v>
       </c>
       <c r="L7" t="n">
         <v>107478</v>
@@ -19789,7 +19789,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>138.37</v>
+        <v>36.8</v>
       </c>
       <c r="L8" t="n">
         <v>155340.9</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>173.45</v>
+        <v>48.18</v>
       </c>
       <c r="L9" t="n">
         <v>198944.1</v>
@@ -19871,7 +19871,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>183.57</v>
+        <v>48.72</v>
       </c>
       <c r="L10" t="n">
         <v>195390.6</v>
@@ -19912,7 +19912,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>137.47</v>
+        <v>34.14</v>
       </c>
       <c r="L11" t="n">
         <v>137340</v>
@@ -19953,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>71.38</v>
+        <v>9.27</v>
       </c>
       <c r="L12" t="n">
         <v>63210</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>28.48</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>32010</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8910</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4860</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1080</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2105436.72</v>
+        <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
         <v>6156486</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3077236.5</v>
+        <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
         <v>10757232</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4646809.2</v>
+        <v>1951659.86</v>
       </c>
       <c r="L7" t="n">
         <v>19346040</v>
@@ -20793,7 +20793,7 @@
         <v>226999.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6718596.61</v>
+        <v>1786860.8</v>
       </c>
       <c r="L8" t="n">
         <v>27961362</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8421941.09</v>
+        <v>2339428.08</v>
       </c>
       <c r="L9" t="n">
         <v>35809938</v>
@@ -20875,7 +20875,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>8913424.92</v>
+        <v>2365648.32</v>
       </c>
       <c r="L10" t="n">
         <v>35170308</v>
@@ -20916,7 +20916,7 @@
         <v>97112</v>
       </c>
       <c r="K11" t="n">
-        <v>6675017.6</v>
+        <v>1657847.51</v>
       </c>
       <c r="L11" t="n">
         <v>24721200</v>
@@ -20957,7 +20957,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>3465878.72</v>
+        <v>450114.12</v>
       </c>
       <c r="L12" t="n">
         <v>11377800</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1383117.66</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>5761800</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>424767.89</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1603800</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95752.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>874800</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>194400</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>70200</v>
@@ -21633,7 +21633,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>401</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
         <v>405750</v>
@@ -21674,7 +21674,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
         <v>284370</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>142680</v>
@@ -21756,7 +21756,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
         <v>94800</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>36870</v>
@@ -21838,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>5850</v>
@@ -22678,7 +22678,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>69.18000000000001</v>
+        <v>17.87</v>
       </c>
       <c r="L5" t="n">
         <v>59717.7</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>56.78</v>
+        <v>18.25</v>
       </c>
       <c r="L6" t="n">
         <v>52791.6</v>
@@ -22760,7 +22760,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>53.59</v>
+        <v>10.85</v>
       </c>
       <c r="L7" t="n">
         <v>56880</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17.66</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>26177.7</v>
@@ -22842,7 +22842,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>4738.5</v>
@@ -23682,7 +23682,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3359055.52</v>
+        <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
         <v>10749186</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2757203.9</v>
+        <v>886244.11</v>
       </c>
       <c r="L6" t="n">
         <v>9502488</v>
@@ -23764,7 +23764,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2602213.15</v>
+        <v>526638.38</v>
       </c>
       <c r="L7" t="n">
         <v>10238400</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>857693.1800000001</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>4711986</v>
@@ -23846,7 +23846,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>852930</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_RedCapacity.xlsx
@@ -560,7 +560,7 @@
         <v>553560</v>
       </c>
       <c r="H4" t="n">
-        <v>64230</v>
+        <v>70560</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>450</v>
       </c>
       <c r="L4" t="n">
-        <v>1465800</v>
+        <v>1547640</v>
       </c>
       <c r="M4" t="n">
-        <v>70500</v>
+        <v>46110</v>
       </c>
       <c r="N4" t="n">
-        <v>78570</v>
+        <v>74400</v>
       </c>
       <c r="O4" t="n">
-        <v>214650</v>
+        <v>218190</v>
       </c>
       <c r="P4" t="n">
-        <v>41910</v>
+        <v>15240</v>
       </c>
       <c r="Q4" t="n">
-        <v>219881.57</v>
+        <v>2278611.47</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>375060</v>
       </c>
       <c r="H5" t="n">
-        <v>54720</v>
+        <v>58890</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
@@ -625,22 +625,22 @@
         <v>267</v>
       </c>
       <c r="L5" t="n">
-        <v>919860</v>
+        <v>984090</v>
       </c>
       <c r="M5" t="n">
-        <v>51960</v>
+        <v>40470</v>
       </c>
       <c r="N5" t="n">
-        <v>80460</v>
+        <v>90630</v>
       </c>
       <c r="O5" t="n">
-        <v>187260</v>
+        <v>213600</v>
       </c>
       <c r="P5" t="n">
-        <v>50190</v>
+        <v>34230</v>
       </c>
       <c r="Q5" t="n">
-        <v>144380.49</v>
+        <v>1496201.06</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>238170</v>
       </c>
       <c r="H6" t="n">
-        <v>42870</v>
+        <v>45840</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>154</v>
       </c>
       <c r="L6" t="n">
-        <v>577860</v>
+        <v>575850</v>
       </c>
       <c r="M6" t="n">
-        <v>36120</v>
+        <v>23850</v>
       </c>
       <c r="N6" t="n">
-        <v>32040</v>
+        <v>44310</v>
       </c>
       <c r="O6" t="n">
-        <v>116940</v>
+        <v>125640</v>
       </c>
       <c r="P6" t="n">
-        <v>49440</v>
+        <v>36990</v>
       </c>
       <c r="Q6" t="n">
-        <v>96380.33</v>
+        <v>998780</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>208140</v>
       </c>
       <c r="H7" t="n">
-        <v>47670</v>
+        <v>49620</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>175</v>
       </c>
       <c r="L7" t="n">
-        <v>541110</v>
+        <v>537330</v>
       </c>
       <c r="M7" t="n">
-        <v>25560</v>
+        <v>25260</v>
       </c>
       <c r="N7" t="n">
-        <v>11970</v>
+        <v>16440</v>
       </c>
       <c r="O7" t="n">
-        <v>86280</v>
+        <v>92130</v>
       </c>
       <c r="P7" t="n">
-        <v>60810</v>
+        <v>44130</v>
       </c>
       <c r="Q7" t="n">
-        <v>91258.78</v>
+        <v>945705.9</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>188100</v>
       </c>
       <c r="H8" t="n">
-        <v>30600</v>
+        <v>30180</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -784,22 +784,22 @@
         <v>109</v>
       </c>
       <c r="L8" t="n">
-        <v>468300</v>
+        <v>458130</v>
       </c>
       <c r="M8" t="n">
-        <v>21300</v>
+        <v>26280</v>
       </c>
       <c r="N8" t="n">
-        <v>2910</v>
+        <v>5610</v>
       </c>
       <c r="O8" t="n">
-        <v>60390</v>
+        <v>68640</v>
       </c>
       <c r="P8" t="n">
-        <v>66420</v>
+        <v>50640</v>
       </c>
       <c r="Q8" t="n">
-        <v>83645.42999999999</v>
+        <v>866809.47</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>154740</v>
       </c>
       <c r="H9" t="n">
-        <v>12180</v>
+        <v>15060</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -837,22 +837,22 @@
         <v>107</v>
       </c>
       <c r="L9" t="n">
-        <v>394560</v>
+        <v>412170</v>
       </c>
       <c r="M9" t="n">
-        <v>13140</v>
+        <v>34560</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>57840</v>
+        <v>62370</v>
       </c>
       <c r="P9" t="n">
-        <v>67290</v>
+        <v>58140</v>
       </c>
       <c r="Q9" t="n">
-        <v>75434.67999999999</v>
+        <v>781722.3</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>160650</v>
       </c>
       <c r="H10" t="n">
-        <v>3870</v>
+        <v>4380</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -890,22 +890,22 @@
         <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>322620</v>
+        <v>347280</v>
       </c>
       <c r="M10" t="n">
-        <v>10560</v>
+        <v>24810</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>41400</v>
+        <v>55350</v>
       </c>
       <c r="P10" t="n">
-        <v>74850</v>
+        <v>73050</v>
       </c>
       <c r="Q10" t="n">
-        <v>68306.12</v>
+        <v>707849.7</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>84690</v>
       </c>
       <c r="H11" t="n">
-        <v>4230</v>
+        <v>4260</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -943,22 +943,22 @@
         <v>42</v>
       </c>
       <c r="L11" t="n">
-        <v>202470</v>
+        <v>240930</v>
       </c>
       <c r="M11" t="n">
-        <v>7140</v>
+        <v>25920</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>14730</v>
+        <v>26520</v>
       </c>
       <c r="P11" t="n">
-        <v>74670</v>
+        <v>87750</v>
       </c>
       <c r="Q11" t="n">
-        <v>43774.77</v>
+        <v>453633.66</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>62460</v>
       </c>
       <c r="H12" t="n">
-        <v>5700</v>
+        <v>5940</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -996,22 +996,22 @@
         <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>153780</v>
+        <v>197970</v>
       </c>
       <c r="M12" t="n">
-        <v>4590</v>
+        <v>23940</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6030</v>
+        <v>15360</v>
       </c>
       <c r="P12" t="n">
-        <v>64740</v>
+        <v>101250</v>
       </c>
       <c r="Q12" t="n">
-        <v>29436.4</v>
+        <v>305046.54</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>52650</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2970</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>120420</v>
+        <v>161520</v>
       </c>
       <c r="M13" t="n">
-        <v>2730</v>
+        <v>16500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>4110</v>
       </c>
       <c r="P13" t="n">
-        <v>44730</v>
+        <v>74550</v>
       </c>
       <c r="Q13" t="n">
-        <v>21207.91</v>
+        <v>219775.48</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>29100</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>49170</v>
+        <v>72360</v>
       </c>
       <c r="M14" t="n">
-        <v>1500</v>
+        <v>19770</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1770</v>
+        <v>2070</v>
       </c>
       <c r="P14" t="n">
-        <v>31710</v>
+        <v>48030</v>
       </c>
       <c r="Q14" t="n">
-        <v>11276.4</v>
+        <v>116856.23</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>9510</v>
       </c>
       <c r="H15" t="n">
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23820</v>
+        <v>37320</v>
       </c>
       <c r="M15" t="n">
-        <v>360</v>
+        <v>6330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2910</v>
       </c>
       <c r="P15" t="n">
-        <v>26670</v>
+        <v>26280</v>
       </c>
       <c r="Q15" t="n">
-        <v>4042.6</v>
+        <v>41893.06</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>4290</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9840</v>
+        <v>26610</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>3780</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>37620</v>
+        <v>47640</v>
       </c>
       <c r="Q16" t="n">
-        <v>2546.71</v>
+        <v>26391.33</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1740</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3150</v>
+        <v>11520</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>2160</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>26310</v>
+        <v>43860</v>
       </c>
       <c r="Q17" t="n">
-        <v>1348.35</v>
+        <v>13972.83</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1500</v>
+        <v>7350</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>870</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>20970</v>
+        <v>29700</v>
       </c>
       <c r="Q18" t="n">
-        <v>636.9</v>
+        <v>6600.15</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>330</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1470</v>
+        <v>4170</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>960</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P19" t="n">
-        <v>18840</v>
+        <v>28650</v>
       </c>
       <c r="Q19" t="n">
-        <v>293.17</v>
+        <v>3038.13</v>
       </c>
     </row>
     <row r="20">
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1020</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6630</v>
+        <v>16530</v>
       </c>
       <c r="Q20" t="n">
-        <v>122.54</v>
+        <v>1269.84</v>
       </c>
     </row>
     <row r="21">
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.87</v>
+        <v>216.27</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="23">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>8220</v>
       </c>
       <c r="H4" t="n">
-        <v>3480</v>
+        <v>3240</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>17010</v>
+        <v>17040</v>
       </c>
       <c r="M4" t="n">
-        <v>3270</v>
+        <v>1260</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>107.7</v>
+        <v>12206.34</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>9030</v>
       </c>
       <c r="H5" t="n">
-        <v>4260</v>
+        <v>4890</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>20250</v>
+        <v>17460</v>
       </c>
       <c r="M5" t="n">
-        <v>6840</v>
+        <v>4710</v>
       </c>
       <c r="N5" t="n">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>203.53</v>
+        <v>23066.28</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8790</v>
       </c>
       <c r="H6" t="n">
-        <v>2640</v>
+        <v>3630</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>20130</v>
+        <v>17670</v>
       </c>
       <c r="M6" t="n">
-        <v>8910</v>
+        <v>4770</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O6" t="n">
         <v>30</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>503.82</v>
+        <v>57099.6</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>7470</v>
       </c>
       <c r="H7" t="n">
-        <v>2820</v>
+        <v>2490</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>24900</v>
+        <v>18480</v>
       </c>
       <c r="M7" t="n">
-        <v>8100</v>
+        <v>4410</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>750</v>
+        <v>390</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>879.4400000000001</v>
+        <v>99670.32000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>12570</v>
       </c>
       <c r="H8" t="n">
-        <v>3990</v>
+        <v>3540</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,22 +2076,22 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>35580</v>
+        <v>28380</v>
       </c>
       <c r="M8" t="n">
-        <v>7410</v>
+        <v>2280</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1191.75</v>
+        <v>135065.34</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>18720</v>
       </c>
       <c r="H9" t="n">
-        <v>4110</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>42000</v>
+        <v>38850</v>
       </c>
       <c r="M9" t="n">
-        <v>3900</v>
+        <v>2610</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1216.35</v>
+        <v>137853</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>20370</v>
       </c>
       <c r="H10" t="n">
-        <v>2940</v>
+        <v>2790</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2182,22 +2182,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>45780</v>
+        <v>47640</v>
       </c>
       <c r="M10" t="n">
-        <v>3180</v>
+        <v>1170</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1301.05</v>
+        <v>147452.22</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>16770</v>
       </c>
       <c r="H11" t="n">
-        <v>3690</v>
+        <v>3480</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,22 +2235,22 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>49320</v>
+        <v>47610</v>
       </c>
       <c r="M11" t="n">
-        <v>2250</v>
+        <v>2520</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1182.65</v>
+        <v>134034.12</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>27930</v>
       </c>
       <c r="H12" t="n">
-        <v>5640</v>
+        <v>5460</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2288,22 +2288,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>83700</v>
+        <v>79800</v>
       </c>
       <c r="M12" t="n">
-        <v>1590</v>
+        <v>4110</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1553.09</v>
+        <v>176017.32</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>31590</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2910</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>85230</v>
+        <v>96960</v>
       </c>
       <c r="M13" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1993.73</v>
+        <v>225956.52</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>20070</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>38520</v>
+        <v>46650</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3990</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1261.55</v>
+        <v>142975.44</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>6900</v>
       </c>
       <c r="H15" t="n">
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18510</v>
+        <v>25080</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>483.33</v>
+        <v>54777.06</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3540</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8460</v>
+        <v>13500</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>2220</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.67</v>
+        <v>39969.72</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2490</v>
+        <v>5970</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>1260</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>134.49</v>
+        <v>15241.86</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>900</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.8</v>
+        <v>7230.78</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.24</v>
+        <v>3313.98</v>
       </c>
     </row>
     <row r="20">
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1020</v>
+        <v>3060</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.23</v>
+        <v>1159.74</v>
       </c>
     </row>
     <row r="21">
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>296.82</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1533.6</v>
+        <v>1760.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>4252.5</v>
+        <v>3666.6</v>
       </c>
       <c r="M5" t="n">
-        <v>136.8</v>
+        <v>94.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.18</v>
+        <v>1153.31</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>439.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1504.8</v>
+        <v>2069.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>7448.1</v>
+        <v>6537.9</v>
       </c>
       <c r="M6" t="n">
-        <v>712.8</v>
+        <v>381.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>7.5</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>377.86</v>
+        <v>42824.7</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1120.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2058.6</v>
+        <v>1817.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>14940</v>
+        <v>11088</v>
       </c>
       <c r="M7" t="n">
-        <v>2835</v>
+        <v>1543.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>262.5</v>
+        <v>136.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>703.5599999999999</v>
+        <v>79736.25999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>8170.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3391.5</v>
+        <v>3009</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>25261.8</v>
+        <v>20149.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4075.5</v>
+        <v>1254</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>175.5</v>
+        <v>297</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1132.17</v>
+        <v>128312.07</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>15912</v>
       </c>
       <c r="H9" t="n">
-        <v>4110</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>34020</v>
+        <v>31468.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2730</v>
+        <v>1827</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>181.5</v>
+        <v>198</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1179.86</v>
+        <v>133717.41</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>20370</v>
       </c>
       <c r="H10" t="n">
-        <v>2940</v>
+        <v>2790</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -3474,22 +3474,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>40744.2</v>
+        <v>42399.6</v>
       </c>
       <c r="M10" t="n">
-        <v>2703</v>
+        <v>994.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1301.05</v>
+        <v>147452.22</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>16770</v>
       </c>
       <c r="H11" t="n">
-        <v>3690</v>
+        <v>3480</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,22 +3527,22 @@
         <v>2.7</v>
       </c>
       <c r="L11" t="n">
-        <v>49320</v>
+        <v>47610</v>
       </c>
       <c r="M11" t="n">
-        <v>2025</v>
+        <v>2268</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>51</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1182.65</v>
+        <v>134034.12</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>27930</v>
       </c>
       <c r="H12" t="n">
-        <v>5640</v>
+        <v>5460</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -3580,22 +3580,22 @@
         <v>4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>83700</v>
+        <v>79800</v>
       </c>
       <c r="M12" t="n">
-        <v>1510.5</v>
+        <v>3904.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1553.09</v>
+        <v>176017.32</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>31590</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2910</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,22 +3633,22 @@
         <v>6.65</v>
       </c>
       <c r="L13" t="n">
-        <v>85230</v>
+        <v>96960</v>
       </c>
       <c r="M13" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1993.73</v>
+        <v>225956.52</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>20070</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>38520</v>
+        <v>46650</v>
       </c>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>3990</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1261.55</v>
+        <v>142975.44</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>6900</v>
       </c>
       <c r="H15" t="n">
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18510</v>
+        <v>25080</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>483.33</v>
+        <v>54777.06</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3540</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8460</v>
+        <v>13500</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>2220</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.67</v>
+        <v>39969.72</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2490</v>
+        <v>5970</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>1260</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>134.49</v>
+        <v>15241.86</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>900</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.8</v>
+        <v>7230.78</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.24</v>
+        <v>3313.98</v>
       </c>
     </row>
     <row r="20">
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1020</v>
+        <v>3060</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.23</v>
+        <v>1159.74</v>
       </c>
     </row>
     <row r="21">
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>296.82</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8741520</v>
+        <v>10034280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>765450</v>
+        <v>659988</v>
       </c>
       <c r="M5" t="n">
-        <v>47880</v>
+        <v>32970</v>
       </c>
       <c r="N5" t="n">
-        <v>408</v>
+        <v>1530</v>
       </c>
       <c r="O5" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6105.78</v>
+        <v>691988.4</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>23733</v>
       </c>
       <c r="H6" t="n">
-        <v>8577360</v>
+        <v>11793870</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>172325.24</v>
       </c>
       <c r="L6" t="n">
-        <v>1340658</v>
+        <v>1176822</v>
       </c>
       <c r="M6" t="n">
-        <v>249480</v>
+        <v>133560</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="O6" t="n">
         <v>1275</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>226719</v>
+        <v>25694820</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>60507</v>
       </c>
       <c r="H7" t="n">
-        <v>11734020</v>
+        <v>10360890</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>2689200</v>
+        <v>1995840</v>
       </c>
       <c r="M7" t="n">
-        <v>992250</v>
+        <v>540225</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>44625</v>
+        <v>23205</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>422133.12</v>
+        <v>47841753.6</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>441207</v>
       </c>
       <c r="H8" t="n">
-        <v>19331550</v>
+        <v>17151300</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,22 +4660,22 @@
         <v>321634.94</v>
       </c>
       <c r="L8" t="n">
-        <v>4547124</v>
+        <v>3626964</v>
       </c>
       <c r="M8" t="n">
-        <v>1426425</v>
+        <v>438900</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>29835</v>
+        <v>50490</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>679299.21</v>
+        <v>76987243.8</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>859248</v>
       </c>
       <c r="H9" t="n">
-        <v>23427000</v>
+        <v>28728000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>467885.62</v>
       </c>
       <c r="L9" t="n">
-        <v>6123600</v>
+        <v>5664330</v>
       </c>
       <c r="M9" t="n">
-        <v>955500</v>
+        <v>639450</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30855</v>
+        <v>33660</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>707915.7</v>
+        <v>80230446</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1099980</v>
       </c>
       <c r="H10" t="n">
-        <v>16758000</v>
+        <v>15903000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -4766,22 +4766,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>7333956</v>
+        <v>7631928</v>
       </c>
       <c r="M10" t="n">
-        <v>946050</v>
+        <v>348075</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17850</v>
+        <v>28560</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>780629.4</v>
+        <v>88471332</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>905580</v>
       </c>
       <c r="H11" t="n">
-        <v>21033000</v>
+        <v>19836000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,22 +4819,22 @@
         <v>130882.7</v>
       </c>
       <c r="L11" t="n">
-        <v>8877600</v>
+        <v>8569800</v>
       </c>
       <c r="M11" t="n">
-        <v>708750</v>
+        <v>793800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8670</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>709592.4</v>
+        <v>80420472</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1508220</v>
       </c>
       <c r="H12" t="n">
-        <v>32148000</v>
+        <v>31122000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -4872,22 +4872,22 @@
         <v>225057.06</v>
       </c>
       <c r="L12" t="n">
-        <v>15066000</v>
+        <v>14364000</v>
       </c>
       <c r="M12" t="n">
-        <v>528675</v>
+        <v>1366575</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>40800</v>
+        <v>30600</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>931856.4</v>
+        <v>105610392</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1705860</v>
       </c>
       <c r="H13" t="n">
-        <v>12312000</v>
+        <v>16587000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,22 +4925,22 @@
         <v>322727.45</v>
       </c>
       <c r="L13" t="n">
-        <v>15341400</v>
+        <v>17452800</v>
       </c>
       <c r="M13" t="n">
-        <v>147000</v>
+        <v>1470000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1196240.4</v>
+        <v>135573912</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>1083780</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4617000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>6933600</v>
+        <v>8397000</v>
       </c>
       <c r="M14" t="n">
-        <v>73500</v>
+        <v>1396500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>756928.8</v>
+        <v>85785264</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>372600</v>
       </c>
       <c r="H15" t="n">
-        <v>3078000</v>
+        <v>4617000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3331800</v>
+        <v>4514400</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>1239000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>289996.2</v>
+        <v>32866236</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>191160</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1522800</v>
+        <v>2430000</v>
       </c>
       <c r="M16" t="n">
-        <v>42000</v>
+        <v>777000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>211604.4</v>
+        <v>23981832</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>48600</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>448200</v>
+        <v>1074600</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>441000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>80692.2</v>
+        <v>9145116</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>162000</v>
+        <v>351000</v>
       </c>
       <c r="M18" t="n">
-        <v>52500</v>
+        <v>178500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38280.6</v>
+        <v>4338468</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>1620</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>118800</v>
+        <v>199800</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>304500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17544.6</v>
+        <v>1988388</v>
       </c>
     </row>
     <row r="20">
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>183600</v>
+        <v>550800</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>724500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6139.8</v>
+        <v>695844</v>
       </c>
     </row>
     <row r="21">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1571.4</v>
+        <v>178092</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.4</v>
+        <v>49572</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>50670</v>
       </c>
       <c r="H4" t="n">
-        <v>9000</v>
+        <v>10170</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>153240</v>
+        <v>171210</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>11640</v>
+        <v>9570</v>
       </c>
       <c r="O4" t="n">
-        <v>20280</v>
+        <v>21570</v>
       </c>
       <c r="P4" t="n">
-        <v>12870</v>
+        <v>9120</v>
       </c>
       <c r="Q4" t="n">
-        <v>29149.07</v>
+        <v>153416.16</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>21540</v>
       </c>
       <c r="H5" t="n">
-        <v>5700</v>
+        <v>6540</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>63030</v>
+        <v>83100</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14910</v>
+        <v>17040</v>
       </c>
       <c r="O5" t="n">
-        <v>10260</v>
+        <v>14580</v>
       </c>
       <c r="P5" t="n">
-        <v>10380</v>
+        <v>14370</v>
       </c>
       <c r="Q5" t="n">
-        <v>13469.33</v>
+        <v>70891.2</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>3180</v>
       </c>
       <c r="H6" t="n">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12690</v>
+        <v>17940</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1680</v>
+        <v>3270</v>
       </c>
       <c r="O6" t="n">
-        <v>450</v>
+        <v>1740</v>
       </c>
       <c r="P6" t="n">
-        <v>6030</v>
+        <v>9480</v>
       </c>
       <c r="Q6" t="n">
-        <v>1666.43</v>
+        <v>8770.68</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>750</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3270</v>
+        <v>5370</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5850</v>
+        <v>8940</v>
       </c>
       <c r="Q7" t="n">
-        <v>134.41</v>
+        <v>707.4</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5040</v>
+        <v>9390</v>
       </c>
       <c r="Q8" t="n">
-        <v>54.38</v>
+        <v>286.2</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>1230</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4380</v>
+        <v>10320</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.24</v>
+        <v>132.84</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2220</v>
+        <v>5850</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.16</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2052</v>
+        <v>2354.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>13236.3</v>
+        <v>17451</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>149.1</v>
+        <v>170.4</v>
       </c>
       <c r="O5" t="n">
-        <v>513</v>
+        <v>729</v>
       </c>
       <c r="P5" t="n">
-        <v>207.6</v>
+        <v>287.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>673.47</v>
+        <v>3544.56</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>159</v>
       </c>
       <c r="H6" t="n">
-        <v>273.6</v>
+        <v>1043.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4695.3</v>
+        <v>6637.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>84</v>
+        <v>163.5</v>
       </c>
       <c r="O6" t="n">
-        <v>112.5</v>
+        <v>435</v>
       </c>
       <c r="P6" t="n">
-        <v>904.5</v>
+        <v>1422</v>
       </c>
       <c r="Q6" t="n">
-        <v>1249.82</v>
+        <v>6578.01</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>112.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1962</v>
+        <v>3222</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1462.5</v>
+        <v>2235</v>
       </c>
       <c r="Q7" t="n">
-        <v>107.52</v>
+        <v>565.92</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1299.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1915.2</v>
+        <v>3568.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.66</v>
+        <v>271.89</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>170.1</v>
+        <v>996.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2190</v>
+        <v>5160</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.48</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>213.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1887</v>
+        <v>4972.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.16</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="11">
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11696400</v>
+        <v>13420080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>2382534</v>
+        <v>3141180</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25347</v>
+        <v>28968</v>
       </c>
       <c r="O5" t="n">
-        <v>87210</v>
+        <v>123930</v>
       </c>
       <c r="P5" t="n">
-        <v>13494</v>
+        <v>18681</v>
       </c>
       <c r="Q5" t="n">
-        <v>404079.84</v>
+        <v>2126736</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>8586</v>
       </c>
       <c r="H6" t="n">
-        <v>1559520</v>
+        <v>5945670</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>845154</v>
+        <v>1194804</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>14280</v>
+        <v>27795</v>
       </c>
       <c r="O6" t="n">
-        <v>19125</v>
+        <v>73950</v>
       </c>
       <c r="P6" t="n">
-        <v>58792.5</v>
+        <v>92430</v>
       </c>
       <c r="Q6" t="n">
-        <v>749893.14</v>
+        <v>3946806</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>6075</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1248300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>353160</v>
+        <v>579960</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>95062.5</v>
+        <v>145275</v>
       </c>
       <c r="Q7" t="n">
-        <v>64514.88</v>
+        <v>339552</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>233874</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>124488</v>
+        <v>231933</v>
       </c>
       <c r="Q8" t="n">
-        <v>30995.46</v>
+        <v>163134</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30618</v>
+        <v>179334</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>142350</v>
+        <v>335400</v>
       </c>
       <c r="Q9" t="n">
-        <v>14689.45</v>
+        <v>77312.88</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>38448</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>122655</v>
+        <v>323212.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8495.280000000001</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="11">
@@ -8707,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1755</v>
+        <v>7020</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>91650</v>
       </c>
       <c r="H4" t="n">
-        <v>6210</v>
+        <v>7140</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>150450</v>
+        <v>169950</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22380</v>
+        <v>23250</v>
       </c>
       <c r="O4" t="n">
-        <v>32760</v>
+        <v>33300</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35185.96</v>
+        <v>190931.58</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>28620</v>
       </c>
       <c r="H5" t="n">
-        <v>4020</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>54210</v>
+        <v>63720</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>9810</v>
+        <v>11970</v>
       </c>
       <c r="O5" t="n">
-        <v>29760</v>
+        <v>30180</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11263.09</v>
+        <v>61117.56</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>9540</v>
       </c>
       <c r="H6" t="n">
-        <v>1530</v>
+        <v>2160</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16860</v>
+        <v>24090</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4890</v>
+        <v>5460</v>
       </c>
       <c r="O6" t="n">
-        <v>25140</v>
+        <v>25500</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2139.37</v>
+        <v>11609.01</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>3060</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4590</v>
+        <v>9210</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2400</v>
+        <v>3660</v>
       </c>
       <c r="O7" t="n">
-        <v>13650</v>
+        <v>17190</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>366.18</v>
+        <v>1987.02</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>960</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2520</v>
+        <v>4680</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>1440</v>
       </c>
       <c r="O8" t="n">
-        <v>3480</v>
+        <v>6360</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>138.28</v>
+        <v>750.33</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>570</v>
+        <v>1110</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.49</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1447.2</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>11384.1</v>
+        <v>13381.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>98.09999999999999</v>
+        <v>119.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1488</v>
+        <v>1509</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>563.15</v>
+        <v>3055.88</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>477</v>
       </c>
       <c r="H6" t="n">
-        <v>872.1</v>
+        <v>1231.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6238.2</v>
+        <v>8913.299999999999</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>244.5</v>
+        <v>273</v>
       </c>
       <c r="O6" t="n">
-        <v>6285</v>
+        <v>6375</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1604.53</v>
+        <v>8706.76</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>459</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2754</v>
+        <v>5526</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>168</v>
+        <v>256.2</v>
       </c>
       <c r="O7" t="n">
-        <v>4777.5</v>
+        <v>6016.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>292.94</v>
+        <v>1589.62</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>624</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1789.2</v>
+        <v>3322.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>66</v>
+        <v>288</v>
       </c>
       <c r="O8" t="n">
-        <v>1566</v>
+        <v>2862</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>131.36</v>
+        <v>712.8099999999999</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.3</v>
+        <v>194.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>313.5</v>
+        <v>610.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.15</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8249040</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>208936.47</v>
       </c>
       <c r="L5" t="n">
-        <v>2049138</v>
+        <v>2408616</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>16677</v>
+        <v>20349</v>
       </c>
       <c r="O5" t="n">
-        <v>252960</v>
+        <v>256530</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>337892.8</v>
+        <v>1833526.8</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>25758</v>
       </c>
       <c r="H6" t="n">
-        <v>4970970</v>
+        <v>7017840</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1122876</v>
+        <v>1604394</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>41565</v>
+        <v>46410</v>
       </c>
       <c r="O6" t="n">
-        <v>1068450</v>
+        <v>1083750</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>962718.62</v>
+        <v>5224054.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>24786</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>495720</v>
+        <v>994680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>28560</v>
+        <v>43554</v>
       </c>
       <c r="O7" t="n">
-        <v>812175</v>
+        <v>1022805</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>175766.11</v>
+        <v>953769.6</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>33696</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>322056</v>
+        <v>598104</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>11220</v>
+        <v>48960</v>
       </c>
       <c r="O8" t="n">
-        <v>266220</v>
+        <v>486540</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78816.81</v>
+        <v>427688.1</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4374</v>
+        <v>34992</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>53295</v>
+        <v>103785</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6689.45</v>
+        <v>36299.34</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>84240</v>
       </c>
       <c r="H4" t="n">
-        <v>7440</v>
+        <v>8130</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -13492,19 +13492,19 @@
         <v>132</v>
       </c>
       <c r="L4" t="n">
-        <v>178200</v>
+        <v>183330</v>
       </c>
       <c r="M4" t="n">
-        <v>10680</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>33060</v>
+        <v>36360</v>
       </c>
       <c r="P4" t="n">
-        <v>17010</v>
+        <v>2760</v>
       </c>
       <c r="Q4" t="n">
         <v>35203.55</v>
@@ -13533,7 +13533,7 @@
         <v>68400</v>
       </c>
       <c r="H5" t="n">
-        <v>5190</v>
+        <v>5760</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -13545,19 +13545,19 @@
         <v>95</v>
       </c>
       <c r="L5" t="n">
-        <v>151410</v>
+        <v>148590</v>
       </c>
       <c r="M5" t="n">
-        <v>17760</v>
+        <v>990</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31410</v>
+        <v>37410</v>
       </c>
       <c r="P5" t="n">
-        <v>25650</v>
+        <v>9360</v>
       </c>
       <c r="Q5" t="n">
         <v>30107</v>
@@ -13586,7 +13586,7 @@
         <v>63000</v>
       </c>
       <c r="H6" t="n">
-        <v>7530</v>
+        <v>7230</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>63</v>
       </c>
       <c r="L6" t="n">
-        <v>149250</v>
+        <v>127890</v>
       </c>
       <c r="M6" t="n">
-        <v>14970</v>
+        <v>1470</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22470</v>
+        <v>23910</v>
       </c>
       <c r="P6" t="n">
-        <v>29520</v>
+        <v>16260</v>
       </c>
       <c r="Q6" t="n">
         <v>27635.4</v>
@@ -13639,7 +13639,7 @@
         <v>83580</v>
       </c>
       <c r="H7" t="n">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>84</v>
       </c>
       <c r="L7" t="n">
-        <v>193470</v>
+        <v>174330</v>
       </c>
       <c r="M7" t="n">
-        <v>10260</v>
+        <v>4110</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>18060</v>
+        <v>16830</v>
       </c>
       <c r="P7" t="n">
-        <v>33990</v>
+        <v>22860</v>
       </c>
       <c r="Q7" t="n">
         <v>39247.82</v>
@@ -13692,7 +13692,7 @@
         <v>70080</v>
       </c>
       <c r="H8" t="n">
-        <v>4230</v>
+        <v>4620</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -13704,19 +13704,19 @@
         <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>155130</v>
+        <v>148350</v>
       </c>
       <c r="M8" t="n">
-        <v>7080</v>
+        <v>5760</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18750</v>
+        <v>19560</v>
       </c>
       <c r="P8" t="n">
-        <v>34170</v>
+        <v>28200</v>
       </c>
       <c r="Q8" t="n">
         <v>37491.69</v>
@@ -13745,7 +13745,7 @@
         <v>37320</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>89160</v>
+        <v>97500</v>
       </c>
       <c r="M9" t="n">
-        <v>4140</v>
+        <v>13260</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>24690</v>
+        <v>22560</v>
       </c>
       <c r="P9" t="n">
-        <v>32730</v>
+        <v>29760</v>
       </c>
       <c r="Q9" t="n">
         <v>30680.85</v>
@@ -13798,7 +13798,7 @@
         <v>30780</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13810,19 +13810,19 @@
         <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>46650</v>
+        <v>52260</v>
       </c>
       <c r="M10" t="n">
-        <v>2070</v>
+        <v>9870</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17460</v>
+        <v>22890</v>
       </c>
       <c r="P10" t="n">
-        <v>35550</v>
+        <v>38940</v>
       </c>
       <c r="Q10" t="n">
         <v>21728.63</v>
@@ -13863,19 +13863,19 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>13080</v>
+        <v>25590</v>
       </c>
       <c r="M11" t="n">
-        <v>960</v>
+        <v>10080</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1890</v>
+        <v>3900</v>
       </c>
       <c r="P11" t="n">
-        <v>33690</v>
+        <v>37560</v>
       </c>
       <c r="Q11" t="n">
         <v>3607.25</v>
@@ -13904,7 +13904,7 @@
         <v>1470</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>34650</v>
       </c>
       <c r="M12" t="n">
-        <v>420</v>
+        <v>10800</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>32640</v>
+        <v>46560</v>
       </c>
       <c r="Q12" t="n">
         <v>538.36</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>21540</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24990</v>
+        <v>43020</v>
       </c>
       <c r="Q13" t="n">
         <v>227.66</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>9780</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>10110</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16620</v>
+        <v>32040</v>
       </c>
       <c r="Q14" t="n">
         <v>180.57</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>2880</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10650</v>
+        <v>9270</v>
       </c>
       <c r="Q15" t="n">
         <v>19.42</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>5640</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>690</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11640</v>
+        <v>17910</v>
       </c>
       <c r="Q16" t="n">
         <v>19.86</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>2850</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12570</v>
+        <v>25740</v>
       </c>
       <c r="Q17" t="n">
         <v>15.4</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>3780</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4560</v>
+        <v>12120</v>
       </c>
       <c r="Q18" t="n">
         <v>7.59</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1110</v>
+        <v>2640</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19699.2</v>
+        <v>21200.4</v>
       </c>
       <c r="I5" t="n">
         <v>2.32</v>
@@ -14837,22 +14837,22 @@
         <v>88.38</v>
       </c>
       <c r="L5" t="n">
-        <v>193170.6</v>
+        <v>206658.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1039.2</v>
+        <v>809.4</v>
       </c>
       <c r="N5" t="n">
-        <v>804.6</v>
+        <v>906.3</v>
       </c>
       <c r="O5" t="n">
-        <v>9363</v>
+        <v>10680</v>
       </c>
       <c r="P5" t="n">
-        <v>1003.8</v>
+        <v>684.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>7219.02</v>
+        <v>74810.05</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11908.5</v>
       </c>
       <c r="H6" t="n">
-        <v>24435.9</v>
+        <v>26128.8</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>78.08</v>
       </c>
       <c r="L6" t="n">
-        <v>213808.2</v>
+        <v>213064.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2889.6</v>
+        <v>1908</v>
       </c>
       <c r="N6" t="n">
-        <v>1602</v>
+        <v>2215.5</v>
       </c>
       <c r="O6" t="n">
-        <v>29235</v>
+        <v>31410</v>
       </c>
       <c r="P6" t="n">
-        <v>7416</v>
+        <v>5548.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>72285.25</v>
+        <v>749085</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>31221</v>
       </c>
       <c r="H7" t="n">
-        <v>34799.1</v>
+        <v>36222.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>111.65</v>
       </c>
       <c r="L7" t="n">
-        <v>324666</v>
+        <v>322398</v>
       </c>
       <c r="M7" t="n">
-        <v>8946</v>
+        <v>8841</v>
       </c>
       <c r="N7" t="n">
-        <v>837.9</v>
+        <v>1150.8</v>
       </c>
       <c r="O7" t="n">
-        <v>30198</v>
+        <v>32245.5</v>
       </c>
       <c r="P7" t="n">
-        <v>15202.5</v>
+        <v>11032.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>73007.02</v>
+        <v>756564.72</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>122265</v>
       </c>
       <c r="H8" t="n">
-        <v>26010</v>
+        <v>25653</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -14996,22 +14996,22 @@
         <v>80.22</v>
       </c>
       <c r="L8" t="n">
-        <v>332493</v>
+        <v>325272.3</v>
       </c>
       <c r="M8" t="n">
-        <v>11715</v>
+        <v>14454</v>
       </c>
       <c r="N8" t="n">
-        <v>582</v>
+        <v>1122</v>
       </c>
       <c r="O8" t="n">
-        <v>27175.5</v>
+        <v>30888</v>
       </c>
       <c r="P8" t="n">
-        <v>25239.6</v>
+        <v>19243.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>79463.16</v>
+        <v>823469</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>131529</v>
       </c>
       <c r="H9" t="n">
-        <v>12180</v>
+        <v>15060</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -15049,22 +15049,22 @@
         <v>85.92</v>
       </c>
       <c r="L9" t="n">
-        <v>319593.6</v>
+        <v>333857.7</v>
       </c>
       <c r="M9" t="n">
-        <v>9198</v>
+        <v>24192</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>31812</v>
+        <v>34303.5</v>
       </c>
       <c r="P9" t="n">
-        <v>33645</v>
+        <v>29070</v>
       </c>
       <c r="Q9" t="n">
-        <v>73171.64</v>
+        <v>758270.63</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>160650</v>
       </c>
       <c r="H10" t="n">
-        <v>3870</v>
+        <v>4380</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -15102,22 +15102,22 @@
         <v>65.25</v>
       </c>
       <c r="L10" t="n">
-        <v>287131.8</v>
+        <v>309079.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8976</v>
+        <v>21088.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>28980</v>
+        <v>38745</v>
       </c>
       <c r="P10" t="n">
-        <v>63622.5</v>
+        <v>62092.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>68306.12</v>
+        <v>707849.7</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>84690</v>
       </c>
       <c r="H11" t="n">
-        <v>4230</v>
+        <v>4260</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -15155,22 +15155,22 @@
         <v>37.74</v>
       </c>
       <c r="L11" t="n">
-        <v>202470</v>
+        <v>240930</v>
       </c>
       <c r="M11" t="n">
-        <v>6426</v>
+        <v>23328</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12520.5</v>
+        <v>22542</v>
       </c>
       <c r="P11" t="n">
-        <v>67203</v>
+        <v>78975</v>
       </c>
       <c r="Q11" t="n">
-        <v>43774.77</v>
+        <v>453633.66</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>62460</v>
       </c>
       <c r="H12" t="n">
-        <v>5700</v>
+        <v>5940</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -15208,22 +15208,22 @@
         <v>16.69</v>
       </c>
       <c r="L12" t="n">
-        <v>153780</v>
+        <v>197970</v>
       </c>
       <c r="M12" t="n">
-        <v>4360.5</v>
+        <v>22743</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6030</v>
+        <v>15360</v>
       </c>
       <c r="P12" t="n">
-        <v>64740</v>
+        <v>101250</v>
       </c>
       <c r="Q12" t="n">
-        <v>29436.4</v>
+        <v>305046.54</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>52650</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2970</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>7.6</v>
       </c>
       <c r="L13" t="n">
-        <v>120420</v>
+        <v>161520</v>
       </c>
       <c r="M13" t="n">
-        <v>2730</v>
+        <v>16500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>4110</v>
       </c>
       <c r="P13" t="n">
-        <v>44730</v>
+        <v>74550</v>
       </c>
       <c r="Q13" t="n">
-        <v>21207.91</v>
+        <v>219775.48</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>29100</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>49170</v>
+        <v>72360</v>
       </c>
       <c r="M14" t="n">
-        <v>1500</v>
+        <v>19770</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1770</v>
+        <v>2070</v>
       </c>
       <c r="P14" t="n">
-        <v>31710</v>
+        <v>48030</v>
       </c>
       <c r="Q14" t="n">
-        <v>11276.4</v>
+        <v>116856.23</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>9510</v>
       </c>
       <c r="H15" t="n">
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23820</v>
+        <v>37320</v>
       </c>
       <c r="M15" t="n">
-        <v>360</v>
+        <v>6330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2910</v>
       </c>
       <c r="P15" t="n">
-        <v>26670</v>
+        <v>26280</v>
       </c>
       <c r="Q15" t="n">
-        <v>4042.6</v>
+        <v>41893.06</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>4290</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9840</v>
+        <v>26610</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>3780</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>37620</v>
+        <v>47640</v>
       </c>
       <c r="Q16" t="n">
-        <v>2546.71</v>
+        <v>26391.33</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1740</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3150</v>
+        <v>11520</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>2160</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>26310</v>
+        <v>43860</v>
       </c>
       <c r="Q17" t="n">
-        <v>1348.35</v>
+        <v>13972.83</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1500</v>
+        <v>7350</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>870</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>20970</v>
+        <v>29700</v>
       </c>
       <c r="Q18" t="n">
-        <v>636.9</v>
+        <v>6600.15</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>330</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1470</v>
+        <v>4170</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>960</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P19" t="n">
-        <v>18840</v>
+        <v>28650</v>
       </c>
       <c r="Q19" t="n">
-        <v>293.17</v>
+        <v>3038.13</v>
       </c>
     </row>
     <row r="20">
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1020</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6630</v>
+        <v>16530</v>
       </c>
       <c r="Q20" t="n">
-        <v>122.54</v>
+        <v>1269.84</v>
       </c>
     </row>
     <row r="21">
@@ -15673,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.87</v>
+        <v>216.27</v>
       </c>
     </row>
     <row r="22">
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="23">
@@ -15791,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1868.4</v>
+        <v>2073.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -16129,19 +16129,19 @@
         <v>31.44</v>
       </c>
       <c r="L5" t="n">
-        <v>31796.1</v>
+        <v>31203.9</v>
       </c>
       <c r="M5" t="n">
-        <v>355.2</v>
+        <v>19.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1570.5</v>
+        <v>1870.5</v>
       </c>
       <c r="P5" t="n">
-        <v>513</v>
+        <v>187.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1505.35</v>
@@ -16170,7 +16170,7 @@
         <v>3150</v>
       </c>
       <c r="H6" t="n">
-        <v>4292.1</v>
+        <v>4121.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>31.94</v>
       </c>
       <c r="L6" t="n">
-        <v>55222.5</v>
+        <v>47319.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1197.6</v>
+        <v>117.6</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5617.5</v>
+        <v>5977.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4428</v>
+        <v>2439</v>
       </c>
       <c r="Q6" t="n">
         <v>20726.55</v>
@@ -16223,7 +16223,7 @@
         <v>12537</v>
       </c>
       <c r="H7" t="n">
-        <v>8979</v>
+        <v>9198</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>53.59</v>
       </c>
       <c r="L7" t="n">
-        <v>116082</v>
+        <v>104598</v>
       </c>
       <c r="M7" t="n">
-        <v>3591</v>
+        <v>1438.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6321</v>
+        <v>5890.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8497.5</v>
+        <v>5715</v>
       </c>
       <c r="Q7" t="n">
         <v>31398.26</v>
@@ -16276,7 +16276,7 @@
         <v>45552</v>
       </c>
       <c r="H8" t="n">
-        <v>3595.5</v>
+        <v>3927</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -16288,19 +16288,19 @@
         <v>36.06</v>
       </c>
       <c r="L8" t="n">
-        <v>110142.3</v>
+        <v>105328.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3894</v>
+        <v>3168</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8437.5</v>
+        <v>8802</v>
       </c>
       <c r="P8" t="n">
-        <v>12984.6</v>
+        <v>10716</v>
       </c>
       <c r="Q8" t="n">
         <v>35617.1</v>
@@ -16329,7 +16329,7 @@
         <v>31722</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>27.3</v>
       </c>
       <c r="L9" t="n">
-        <v>72219.60000000001</v>
+        <v>78975</v>
       </c>
       <c r="M9" t="n">
-        <v>2898</v>
+        <v>9282</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>13579.5</v>
+        <v>12408</v>
       </c>
       <c r="P9" t="n">
-        <v>16365</v>
+        <v>14880</v>
       </c>
       <c r="Q9" t="n">
         <v>29760.42</v>
@@ -16382,7 +16382,7 @@
         <v>30780</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16394,19 +16394,19 @@
         <v>13.05</v>
       </c>
       <c r="L10" t="n">
-        <v>41518.5</v>
+        <v>46511.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1759.5</v>
+        <v>8389.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12222</v>
+        <v>16023</v>
       </c>
       <c r="P10" t="n">
-        <v>30217.5</v>
+        <v>33099</v>
       </c>
       <c r="Q10" t="n">
         <v>21728.63</v>
@@ -16447,19 +16447,19 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>13080</v>
+        <v>25590</v>
       </c>
       <c r="M11" t="n">
-        <v>864</v>
+        <v>9072</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1606.5</v>
+        <v>3315</v>
       </c>
       <c r="P11" t="n">
-        <v>30321</v>
+        <v>33804</v>
       </c>
       <c r="Q11" t="n">
         <v>3607.25</v>
@@ -16488,7 +16488,7 @@
         <v>1470</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>2.78</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>34650</v>
       </c>
       <c r="M12" t="n">
-        <v>399</v>
+        <v>10260</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>32640</v>
+        <v>46560</v>
       </c>
       <c r="Q12" t="n">
         <v>538.36</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>21540</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24990</v>
+        <v>43020</v>
       </c>
       <c r="Q13" t="n">
         <v>227.66</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>9780</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>10110</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16620</v>
+        <v>32040</v>
       </c>
       <c r="Q14" t="n">
         <v>180.57</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>2880</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10650</v>
+        <v>9270</v>
       </c>
       <c r="Q15" t="n">
         <v>19.42</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>5640</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>690</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11640</v>
+        <v>17910</v>
       </c>
       <c r="Q16" t="n">
         <v>19.86</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>2850</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12570</v>
+        <v>25740</v>
       </c>
       <c r="Q17" t="n">
         <v>15.4</v>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>3780</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4560</v>
+        <v>12120</v>
       </c>
       <c r="Q18" t="n">
         <v>7.59</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1110</v>
+        <v>2640</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10649880</v>
+        <v>11819520</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -17421,19 +17421,19 @@
         <v>1526843.42</v>
       </c>
       <c r="L5" t="n">
-        <v>5723298</v>
+        <v>5616702</v>
       </c>
       <c r="M5" t="n">
-        <v>124320</v>
+        <v>6930</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>266985</v>
+        <v>317985</v>
       </c>
       <c r="P5" t="n">
-        <v>33345</v>
+        <v>12168</v>
       </c>
       <c r="Q5" t="n">
         <v>903210.05</v>
@@ -17462,7 +17462,7 @@
         <v>170100</v>
       </c>
       <c r="H6" t="n">
-        <v>24464970</v>
+        <v>23490270</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1550927.2</v>
       </c>
       <c r="L6" t="n">
-        <v>9940050</v>
+        <v>8517474</v>
       </c>
       <c r="M6" t="n">
-        <v>419160</v>
+        <v>41160</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>954975</v>
+        <v>1016175</v>
       </c>
       <c r="P6" t="n">
-        <v>287820</v>
+        <v>158535</v>
       </c>
       <c r="Q6" t="n">
         <v>12435928.38</v>
@@ -17515,7 +17515,7 @@
         <v>676998</v>
       </c>
       <c r="H7" t="n">
-        <v>51180300</v>
+        <v>52428600</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2602213.15</v>
       </c>
       <c r="L7" t="n">
-        <v>20894760</v>
+        <v>18827640</v>
       </c>
       <c r="M7" t="n">
-        <v>1256850</v>
+        <v>503475</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1074570</v>
+        <v>1001385</v>
       </c>
       <c r="P7" t="n">
-        <v>552337.5</v>
+        <v>371475</v>
       </c>
       <c r="Q7" t="n">
         <v>18838954.94</v>
@@ -17568,7 +17568,7 @@
         <v>2459808</v>
       </c>
       <c r="H8" t="n">
-        <v>20494350</v>
+        <v>22383900</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -17580,19 +17580,19 @@
         <v>1751123.58</v>
       </c>
       <c r="L8" t="n">
-        <v>19825614</v>
+        <v>18959130</v>
       </c>
       <c r="M8" t="n">
-        <v>1362900</v>
+        <v>1108800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1434375</v>
+        <v>1496340</v>
       </c>
       <c r="P8" t="n">
-        <v>843999</v>
+        <v>696540</v>
       </c>
       <c r="Q8" t="n">
         <v>21370260.56</v>
@@ -17621,7 +17621,7 @@
         <v>1712988</v>
       </c>
       <c r="H9" t="n">
-        <v>2907000</v>
+        <v>4104000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
-        <v>12999528</v>
+        <v>14215500</v>
       </c>
       <c r="M9" t="n">
-        <v>1014300</v>
+        <v>3248700</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2308515</v>
+        <v>2109360</v>
       </c>
       <c r="P9" t="n">
-        <v>1063725</v>
+        <v>967200</v>
       </c>
       <c r="Q9" t="n">
         <v>17856254</v>
@@ -17674,7 +17674,7 @@
         <v>1662120</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -17686,19 +17686,19 @@
         <v>633655.8</v>
       </c>
       <c r="L10" t="n">
-        <v>7473330</v>
+        <v>8372052</v>
       </c>
       <c r="M10" t="n">
-        <v>615825</v>
+        <v>2936325</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2077740</v>
+        <v>2723910</v>
       </c>
       <c r="P10" t="n">
-        <v>1964137.5</v>
+        <v>2151435</v>
       </c>
       <c r="Q10" t="n">
         <v>13037178.96</v>
@@ -17739,19 +17739,19 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>2354400</v>
+        <v>4606200</v>
       </c>
       <c r="M11" t="n">
-        <v>302400</v>
+        <v>3175200</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>273105</v>
+        <v>563550</v>
       </c>
       <c r="P11" t="n">
-        <v>1970865</v>
+        <v>2197260</v>
       </c>
       <c r="Q11" t="n">
         <v>2164348.08</v>
@@ -17780,7 +17780,7 @@
         <v>79380</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>135034.24</v>
       </c>
       <c r="L12" t="n">
-        <v>1085400</v>
+        <v>6237000</v>
       </c>
       <c r="M12" t="n">
-        <v>139650</v>
+        <v>3591000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>2121600</v>
+        <v>3026400</v>
       </c>
       <c r="Q12" t="n">
         <v>323015.04</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>561600</v>
+        <v>3877200</v>
       </c>
       <c r="M13" t="n">
-        <v>63000</v>
+        <v>1774500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1624350</v>
+        <v>2796300</v>
       </c>
       <c r="Q13" t="n">
         <v>136598.4</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>232200</v>
+        <v>1760400</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>3538500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1080300</v>
+        <v>2082600</v>
       </c>
       <c r="Q14" t="n">
         <v>108341.28</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>91800</v>
+        <v>518400</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>357000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>692250</v>
+        <v>602550</v>
       </c>
       <c r="Q15" t="n">
         <v>11651.04</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>1015200</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>241500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>756600</v>
+        <v>1164150</v>
       </c>
       <c r="Q16" t="n">
         <v>11918.88</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>48600</v>
+        <v>513000</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>817050</v>
+        <v>1673100</v>
       </c>
       <c r="Q17" t="n">
         <v>9240.48</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>91800</v>
+        <v>680400</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>296400</v>
+        <v>787800</v>
       </c>
       <c r="Q18" t="n">
         <v>4553.28</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>108000</v>
+        <v>286200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>72150</v>
+        <v>171600</v>
       </c>
       <c r="Q19" t="n">
         <v>1740.96</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>117270</v>
       </c>
       <c r="H4" t="n">
-        <v>14850</v>
+        <v>16440</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>374610</v>
+        <v>414240</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16350</v>
+        <v>13410</v>
       </c>
       <c r="O4" t="n">
-        <v>54600</v>
+        <v>52920</v>
       </c>
       <c r="P4" t="n">
-        <v>7680</v>
+        <v>2520</v>
       </c>
       <c r="Q4" t="n">
-        <v>36998.21</v>
+        <v>423937.8</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>35280</v>
       </c>
       <c r="H5" t="n">
-        <v>3180</v>
+        <v>5730</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>125790</v>
+        <v>156390</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25890</v>
+        <v>29310</v>
       </c>
       <c r="O5" t="n">
-        <v>36750</v>
+        <v>50310</v>
       </c>
       <c r="P5" t="n">
-        <v>6510</v>
+        <v>8340</v>
       </c>
       <c r="Q5" t="n">
-        <v>13033.87</v>
+        <v>149346.45</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4980</v>
       </c>
       <c r="H6" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21270</v>
+        <v>32730</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7260</v>
+        <v>12360</v>
       </c>
       <c r="O6" t="n">
-        <v>7590</v>
+        <v>10380</v>
       </c>
       <c r="P6" t="n">
-        <v>4140</v>
+        <v>7950</v>
       </c>
       <c r="Q6" t="n">
-        <v>1293.06</v>
+        <v>14816.34</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3720</v>
+        <v>9030</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="O7" t="n">
-        <v>2520</v>
+        <v>3450</v>
       </c>
       <c r="P7" t="n">
-        <v>3600</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>166.84</v>
+        <v>1911.69</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>720</v>
+        <v>1860</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>720</v>
+        <v>1410</v>
       </c>
       <c r="P8" t="n">
-        <v>1980</v>
+        <v>6450</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.95</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1144.8</v>
+        <v>2062.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>5.63</v>
       </c>
       <c r="L5" t="n">
-        <v>26415.9</v>
+        <v>32841.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>258.9</v>
+        <v>293.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1837.5</v>
+        <v>2515.5</v>
       </c>
       <c r="P5" t="n">
-        <v>130.2</v>
+        <v>166.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>651.6900000000001</v>
+        <v>7467.32</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>249</v>
       </c>
       <c r="H6" t="n">
-        <v>222.3</v>
+        <v>307.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7869.9</v>
+        <v>12110.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>363</v>
+        <v>618</v>
       </c>
       <c r="O6" t="n">
-        <v>1897.5</v>
+        <v>2595</v>
       </c>
       <c r="P6" t="n">
-        <v>621</v>
+        <v>1192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>969.8</v>
+        <v>11112.26</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2232</v>
+        <v>5418</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14.7</v>
+        <v>35.7</v>
       </c>
       <c r="O7" t="n">
-        <v>882</v>
+        <v>1207.5</v>
       </c>
       <c r="P7" t="n">
-        <v>900</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>133.47</v>
+        <v>1529.35</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>511.2</v>
+        <v>1320.6</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>324</v>
+        <v>634.5</v>
       </c>
       <c r="P8" t="n">
-        <v>752.4</v>
+        <v>2451</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.2</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6525360</v>
+        <v>11757960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>273224.61</v>
       </c>
       <c r="L5" t="n">
-        <v>4754862</v>
+        <v>5911542</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>44013</v>
+        <v>49827</v>
       </c>
       <c r="O5" t="n">
-        <v>312375</v>
+        <v>427635</v>
       </c>
       <c r="P5" t="n">
-        <v>8463</v>
+        <v>10842</v>
       </c>
       <c r="Q5" t="n">
-        <v>391016.16</v>
+        <v>4480393.5</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>13446</v>
       </c>
       <c r="H6" t="n">
-        <v>1267110</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1416582</v>
+        <v>2179818</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>61710</v>
+        <v>105060</v>
       </c>
       <c r="O6" t="n">
-        <v>322575</v>
+        <v>441150</v>
       </c>
       <c r="P6" t="n">
-        <v>40365</v>
+        <v>77512.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>581878.08</v>
+        <v>6667353</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>401760</v>
+        <v>975240</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2499</v>
+        <v>6069</v>
       </c>
       <c r="O7" t="n">
-        <v>149940</v>
+        <v>205275</v>
       </c>
       <c r="P7" t="n">
-        <v>58500</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>80082.42999999999</v>
+        <v>917611.2</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>92016</v>
+        <v>237708</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>55080</v>
+        <v>107865</v>
       </c>
       <c r="P8" t="n">
-        <v>48906</v>
+        <v>159315</v>
       </c>
       <c r="Q8" t="n">
-        <v>8519.9</v>
+        <v>97623.89999999999</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>112285440</v>
+        <v>120842280</v>
       </c>
       <c r="I5" t="n">
         <v>450017.01</v>
@@ -22589,22 +22589,22 @@
         <v>4291233.61</v>
       </c>
       <c r="L5" t="n">
-        <v>34770708</v>
+        <v>37198602</v>
       </c>
       <c r="M5" t="n">
-        <v>363720</v>
+        <v>283290</v>
       </c>
       <c r="N5" t="n">
-        <v>136782</v>
+        <v>154071</v>
       </c>
       <c r="O5" t="n">
-        <v>1591710</v>
+        <v>1815600</v>
       </c>
       <c r="P5" t="n">
-        <v>65247</v>
+        <v>44499</v>
       </c>
       <c r="Q5" t="n">
-        <v>4331414.74</v>
+        <v>44886031.74</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>643059</v>
       </c>
       <c r="H6" t="n">
-        <v>139284630</v>
+        <v>148934160</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>3791155.37</v>
       </c>
       <c r="L6" t="n">
-        <v>38485476</v>
+        <v>38351610</v>
       </c>
       <c r="M6" t="n">
-        <v>1011360</v>
+        <v>667800</v>
       </c>
       <c r="N6" t="n">
-        <v>272340</v>
+        <v>376635</v>
       </c>
       <c r="O6" t="n">
-        <v>4969950</v>
+        <v>5339700</v>
       </c>
       <c r="P6" t="n">
-        <v>482040</v>
+        <v>360652.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>43371147.06</v>
+        <v>449450999.78</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1685934</v>
       </c>
       <c r="H7" t="n">
-        <v>198354870</v>
+        <v>206468820</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>5421277.4</v>
       </c>
       <c r="L7" t="n">
-        <v>58439880</v>
+        <v>58031640</v>
       </c>
       <c r="M7" t="n">
-        <v>3131100</v>
+        <v>3094350</v>
       </c>
       <c r="N7" t="n">
-        <v>142443</v>
+        <v>195636</v>
       </c>
       <c r="O7" t="n">
-        <v>5133660</v>
+        <v>5481735</v>
       </c>
       <c r="P7" t="n">
-        <v>988162.5</v>
+        <v>717112.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>43804214.21</v>
+        <v>453938832.72</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6602310</v>
       </c>
       <c r="H8" t="n">
-        <v>148257000</v>
+        <v>146222100</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -22748,22 +22748,22 @@
         <v>3895356.54</v>
       </c>
       <c r="L8" t="n">
-        <v>59848740</v>
+        <v>58549014</v>
       </c>
       <c r="M8" t="n">
-        <v>4100250</v>
+        <v>5058900</v>
       </c>
       <c r="N8" t="n">
-        <v>98940</v>
+        <v>190740</v>
       </c>
       <c r="O8" t="n">
-        <v>4619835</v>
+        <v>5250960</v>
       </c>
       <c r="P8" t="n">
-        <v>1640574</v>
+        <v>1250808</v>
       </c>
       <c r="Q8" t="n">
-        <v>47677893.73</v>
+        <v>494081398.76</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7102566</v>
       </c>
       <c r="H9" t="n">
-        <v>69426000</v>
+        <v>85842000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -22801,22 +22801,22 @@
         <v>4171980.08</v>
       </c>
       <c r="L9" t="n">
-        <v>57526848</v>
+        <v>60094386</v>
       </c>
       <c r="M9" t="n">
-        <v>3219300</v>
+        <v>8467200</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>5408040</v>
+        <v>5831595</v>
       </c>
       <c r="P9" t="n">
-        <v>2186925</v>
+        <v>1889550</v>
       </c>
       <c r="Q9" t="n">
-        <v>43902984.23</v>
+        <v>454962376.85</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>8675100</v>
       </c>
       <c r="H10" t="n">
-        <v>22059000</v>
+        <v>24966000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -22854,22 +22854,22 @@
         <v>3168279</v>
       </c>
       <c r="L10" t="n">
-        <v>51683724</v>
+        <v>55634256</v>
       </c>
       <c r="M10" t="n">
-        <v>3141600</v>
+        <v>7380975</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4926600</v>
+        <v>6586650</v>
       </c>
       <c r="P10" t="n">
-        <v>4135462.5</v>
+        <v>4036012.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>40983671.52</v>
+        <v>424709821.8</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4573260</v>
       </c>
       <c r="H11" t="n">
-        <v>24111000</v>
+        <v>24282000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -22907,22 +22907,22 @@
         <v>1832357.77</v>
       </c>
       <c r="L11" t="n">
-        <v>36444600</v>
+        <v>43367400</v>
       </c>
       <c r="M11" t="n">
-        <v>2249100</v>
+        <v>8164800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2128485</v>
+        <v>3832140</v>
       </c>
       <c r="P11" t="n">
-        <v>4368195</v>
+        <v>5133375</v>
       </c>
       <c r="Q11" t="n">
-        <v>26264859.12</v>
+        <v>272180193.3</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3372840</v>
       </c>
       <c r="H12" t="n">
-        <v>32490000</v>
+        <v>33858000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -22960,22 +22960,22 @@
         <v>810205.42</v>
       </c>
       <c r="L12" t="n">
-        <v>27680400</v>
+        <v>35634600</v>
       </c>
       <c r="M12" t="n">
-        <v>1526175</v>
+        <v>7960050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1025100</v>
+        <v>2611200</v>
       </c>
       <c r="P12" t="n">
-        <v>4208100</v>
+        <v>6581250</v>
       </c>
       <c r="Q12" t="n">
-        <v>17661838.32</v>
+        <v>183027921.3</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2843100</v>
       </c>
       <c r="H13" t="n">
-        <v>12312000</v>
+        <v>16929000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>368831.38</v>
       </c>
       <c r="L13" t="n">
-        <v>21675600</v>
+        <v>29073600</v>
       </c>
       <c r="M13" t="n">
-        <v>955500</v>
+        <v>5775000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>418200</v>
+        <v>698700</v>
       </c>
       <c r="P13" t="n">
-        <v>2907450</v>
+        <v>4845750</v>
       </c>
       <c r="Q13" t="n">
-        <v>12724743.6</v>
+        <v>131865286.5</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1571400</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4617000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>8850600</v>
+        <v>13024800</v>
       </c>
       <c r="M14" t="n">
-        <v>525000</v>
+        <v>6919500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>300900</v>
+        <v>351900</v>
       </c>
       <c r="P14" t="n">
-        <v>2061150</v>
+        <v>3121950</v>
       </c>
       <c r="Q14" t="n">
-        <v>6765839.28</v>
+        <v>70113737.7</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>513540</v>
       </c>
       <c r="H15" t="n">
-        <v>3078000</v>
+        <v>4617000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4287600</v>
+        <v>6717600</v>
       </c>
       <c r="M15" t="n">
-        <v>126000</v>
+        <v>2215500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>459000</v>
+        <v>494700</v>
       </c>
       <c r="P15" t="n">
-        <v>1733550</v>
+        <v>1708200</v>
       </c>
       <c r="Q15" t="n">
-        <v>2425559.04</v>
+        <v>25135833.6</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>231660</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1771200</v>
+        <v>4789800</v>
       </c>
       <c r="M16" t="n">
-        <v>73500</v>
+        <v>1323000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>20400</v>
+        <v>86700</v>
       </c>
       <c r="P16" t="n">
-        <v>2445300</v>
+        <v>3096600</v>
       </c>
       <c r="Q16" t="n">
-        <v>1528027.2</v>
+        <v>15834798</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>93960</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>567000</v>
+        <v>2073600</v>
       </c>
       <c r="M17" t="n">
-        <v>63000</v>
+        <v>756000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1710150</v>
+        <v>2850900</v>
       </c>
       <c r="Q17" t="n">
-        <v>809010.72</v>
+        <v>8383699.8</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>270000</v>
+        <v>1323000</v>
       </c>
       <c r="M18" t="n">
-        <v>63000</v>
+        <v>304500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1363050</v>
+        <v>1930500</v>
       </c>
       <c r="Q18" t="n">
-        <v>382140.72</v>
+        <v>3960087.3</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>17820</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>264600</v>
+        <v>750600</v>
       </c>
       <c r="M19" t="n">
-        <v>42000</v>
+        <v>336000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5100</v>
+        <v>15300</v>
       </c>
       <c r="P19" t="n">
-        <v>1224600</v>
+        <v>1862250</v>
       </c>
       <c r="Q19" t="n">
-        <v>175903.92</v>
+        <v>1822875.3</v>
       </c>
     </row>
     <row r="20">
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>183600</v>
+        <v>610200</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>756000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>430950</v>
+        <v>1074450</v>
       </c>
       <c r="Q20" t="n">
-        <v>73522.08</v>
+        <v>761902.2</v>
       </c>
     </row>
     <row r="21">
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>12521.52</v>
+        <v>129759.3</v>
       </c>
     </row>
     <row r="22">
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2075.76</v>
+        <v>21510.9</v>
       </c>
     </row>
     <row r="23">
@@ -23543,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -23816,7 +23816,7 @@
         <v>45900</v>
       </c>
       <c r="H4" t="n">
-        <v>2910</v>
+        <v>2460</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>131460</v>
+        <v>112110</v>
       </c>
       <c r="M4" t="n">
-        <v>45570</v>
+        <v>42720</v>
       </c>
       <c r="N4" t="n">
-        <v>10950</v>
+        <v>9180</v>
       </c>
       <c r="O4" t="n">
-        <v>16110</v>
+        <v>19410</v>
       </c>
       <c r="P4" t="n">
-        <v>1800</v>
+        <v>480</v>
       </c>
       <c r="Q4" t="n">
-        <v>9472.57</v>
+        <v>92868.3</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>61500</v>
       </c>
       <c r="H5" t="n">
-        <v>6480</v>
+        <v>5250</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -23881,22 +23881,22 @@
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>162870</v>
+        <v>148110</v>
       </c>
       <c r="M5" t="n">
-        <v>19980</v>
+        <v>31170</v>
       </c>
       <c r="N5" t="n">
-        <v>20820</v>
+        <v>20100</v>
       </c>
       <c r="O5" t="n">
-        <v>19590</v>
+        <v>20010</v>
       </c>
       <c r="P5" t="n">
-        <v>2670</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>17699.04</v>
+        <v>173520</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>64620</v>
       </c>
       <c r="H6" t="n">
-        <v>12870</v>
+        <v>13620</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>48</v>
       </c>
       <c r="L6" t="n">
-        <v>161520</v>
+        <v>152220</v>
       </c>
       <c r="M6" t="n">
-        <v>8880</v>
+        <v>14790</v>
       </c>
       <c r="N6" t="n">
-        <v>15720</v>
+        <v>18630</v>
       </c>
       <c r="O6" t="n">
-        <v>20070</v>
+        <v>22380</v>
       </c>
       <c r="P6" t="n">
-        <v>2970</v>
+        <v>1110</v>
       </c>
       <c r="Q6" t="n">
-        <v>21197.91</v>
+        <v>207822.6</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>57960</v>
       </c>
       <c r="H7" t="n">
-        <v>12990</v>
+        <v>13380</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>63</v>
       </c>
       <c r="L7" t="n">
-        <v>179130</v>
+        <v>181530</v>
       </c>
       <c r="M7" t="n">
-        <v>4950</v>
+        <v>13140</v>
       </c>
       <c r="N7" t="n">
-        <v>8040</v>
+        <v>9930</v>
       </c>
       <c r="O7" t="n">
-        <v>19800</v>
+        <v>19440</v>
       </c>
       <c r="P7" t="n">
-        <v>4290</v>
+        <v>1620</v>
       </c>
       <c r="Q7" t="n">
-        <v>22747.12</v>
+        <v>223011</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>80160</v>
       </c>
       <c r="H8" t="n">
-        <v>19830</v>
+        <v>18690</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>218790</v>
+        <v>210000</v>
       </c>
       <c r="M8" t="n">
-        <v>4860</v>
+        <v>12750</v>
       </c>
       <c r="N8" t="n">
-        <v>2430</v>
+        <v>3360</v>
       </c>
       <c r="O8" t="n">
-        <v>21900</v>
+        <v>23100</v>
       </c>
       <c r="P8" t="n">
-        <v>5430</v>
+        <v>3180</v>
       </c>
       <c r="Q8" t="n">
-        <v>23117.26</v>
+        <v>226639.8</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>92400</v>
       </c>
       <c r="H9" t="n">
-        <v>7140</v>
+        <v>8760</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -24093,22 +24093,22 @@
         <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>245610</v>
+        <v>254640</v>
       </c>
       <c r="M9" t="n">
-        <v>4740</v>
+        <v>11520</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20520</v>
+        <v>22050</v>
       </c>
       <c r="P9" t="n">
-        <v>8640</v>
+        <v>6240</v>
       </c>
       <c r="Q9" t="n">
-        <v>27409.92</v>
+        <v>268724.7</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>104820</v>
       </c>
       <c r="H10" t="n">
-        <v>870</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>219540</v>
+        <v>232830</v>
       </c>
       <c r="M10" t="n">
-        <v>5130</v>
+        <v>8760</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21360</v>
+        <v>24510</v>
       </c>
       <c r="P10" t="n">
-        <v>11580</v>
+        <v>6630</v>
       </c>
       <c r="Q10" t="n">
-        <v>30205.78</v>
+        <v>296135.1</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>62820</v>
       </c>
       <c r="H11" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>137340</v>
+        <v>158790</v>
       </c>
       <c r="M11" t="n">
-        <v>3750</v>
+        <v>8100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12570</v>
+        <v>20160</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>7440</v>
       </c>
       <c r="Q11" t="n">
-        <v>26491.46</v>
+        <v>259720.2</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>32670</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>63210</v>
+        <v>78660</v>
       </c>
       <c r="M12" t="n">
-        <v>2550</v>
+        <v>5100</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5910</v>
+        <v>15060</v>
       </c>
       <c r="P12" t="n">
-        <v>15420</v>
+        <v>15390</v>
       </c>
       <c r="Q12" t="n">
-        <v>17073.06</v>
+        <v>167382.9</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>32010</v>
+        <v>41490</v>
       </c>
       <c r="M13" t="n">
-        <v>2100</v>
+        <v>4620</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>4080</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>12960</v>
       </c>
       <c r="Q13" t="n">
-        <v>9615.59</v>
+        <v>94270.5</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8910</v>
+        <v>15120</v>
       </c>
       <c r="M14" t="n">
-        <v>1140</v>
+        <v>5220</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1770</v>
+        <v>2070</v>
       </c>
       <c r="P14" t="n">
-        <v>12840</v>
+        <v>12180</v>
       </c>
       <c r="Q14" t="n">
-        <v>4232.16</v>
+        <v>41491.8</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4860</v>
+        <v>9390</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>1800</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2910</v>
       </c>
       <c r="P15" t="n">
-        <v>15300</v>
+        <v>15630</v>
       </c>
       <c r="Q15" t="n">
-        <v>1299.52</v>
+        <v>12740.4</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1080</v>
+        <v>7470</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>25980</v>
+        <v>29730</v>
       </c>
       <c r="Q16" t="n">
-        <v>559.7</v>
+        <v>5487.3</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2700</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13740</v>
+        <v>18120</v>
       </c>
       <c r="Q17" t="n">
-        <v>225</v>
+        <v>2205.9</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>16440</v>
+        <v>17610</v>
       </c>
       <c r="Q18" t="n">
-        <v>123.47</v>
+        <v>1210.5</v>
       </c>
     </row>
     <row r="19">
@@ -24623,22 +24623,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>210</v>
+        <v>1470</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P19" t="n">
-        <v>17730</v>
+        <v>26010</v>
       </c>
       <c r="Q19" t="n">
-        <v>99.51000000000001</v>
+        <v>975.6</v>
       </c>
     </row>
     <row r="20">
@@ -24676,10 +24676,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6630</v>
+        <v>16530</v>
       </c>
       <c r="Q20" t="n">
-        <v>44.98</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21">
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.37</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2332.8</v>
+        <v>1890</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -25173,22 +25173,22 @@
         <v>22.18</v>
       </c>
       <c r="L5" t="n">
-        <v>34202.7</v>
+        <v>31103.1</v>
       </c>
       <c r="M5" t="n">
-        <v>399.6</v>
+        <v>623.4</v>
       </c>
       <c r="N5" t="n">
-        <v>208.2</v>
+        <v>201</v>
       </c>
       <c r="O5" t="n">
-        <v>979.5</v>
+        <v>1000.5</v>
       </c>
       <c r="P5" t="n">
-        <v>53.4</v>
+        <v>16.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>884.95</v>
+        <v>8676</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3231</v>
       </c>
       <c r="H6" t="n">
-        <v>7335.9</v>
+        <v>7763.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>24.34</v>
       </c>
       <c r="L6" t="n">
-        <v>59762.4</v>
+        <v>56321.4</v>
       </c>
       <c r="M6" t="n">
-        <v>710.4</v>
+        <v>1183.2</v>
       </c>
       <c r="N6" t="n">
-        <v>786</v>
+        <v>931.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5017.5</v>
+        <v>5595</v>
       </c>
       <c r="P6" t="n">
-        <v>445.5</v>
+        <v>166.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>15898.43</v>
+        <v>155866.95</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>8694</v>
       </c>
       <c r="H7" t="n">
-        <v>9482.700000000001</v>
+        <v>9767.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>40.19</v>
       </c>
       <c r="L7" t="n">
-        <v>107478</v>
+        <v>108918</v>
       </c>
       <c r="M7" t="n">
-        <v>1732.5</v>
+        <v>4599</v>
       </c>
       <c r="N7" t="n">
-        <v>562.8</v>
+        <v>695.1</v>
       </c>
       <c r="O7" t="n">
-        <v>6930</v>
+        <v>6804</v>
       </c>
       <c r="P7" t="n">
-        <v>1072.5</v>
+        <v>405</v>
       </c>
       <c r="Q7" t="n">
-        <v>18197.7</v>
+        <v>178408.8</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>52104</v>
       </c>
       <c r="H8" t="n">
-        <v>16855.5</v>
+        <v>15886.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>36.8</v>
       </c>
       <c r="L8" t="n">
-        <v>155340.9</v>
+        <v>149100</v>
       </c>
       <c r="M8" t="n">
-        <v>2673</v>
+        <v>7012.5</v>
       </c>
       <c r="N8" t="n">
-        <v>486</v>
+        <v>672</v>
       </c>
       <c r="O8" t="n">
-        <v>9855</v>
+        <v>10395</v>
       </c>
       <c r="P8" t="n">
-        <v>2063.4</v>
+        <v>1208.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>21961.4</v>
+        <v>215307.81</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>78540</v>
       </c>
       <c r="H9" t="n">
-        <v>7140</v>
+        <v>8760</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -25385,22 +25385,22 @@
         <v>48.18</v>
       </c>
       <c r="L9" t="n">
-        <v>198944.1</v>
+        <v>206258.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3318</v>
+        <v>8064</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11286</v>
+        <v>12127.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>3120</v>
       </c>
       <c r="Q9" t="n">
-        <v>26587.62</v>
+        <v>260662.96</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>104820</v>
       </c>
       <c r="H10" t="n">
-        <v>870</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>48.72</v>
       </c>
       <c r="L10" t="n">
-        <v>195390.6</v>
+        <v>207218.7</v>
       </c>
       <c r="M10" t="n">
-        <v>4360.5</v>
+        <v>7446</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14952</v>
+        <v>17157</v>
       </c>
       <c r="P10" t="n">
-        <v>9843</v>
+        <v>5635.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>30205.78</v>
+        <v>296135.1</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>62820</v>
       </c>
       <c r="H11" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>34.14</v>
       </c>
       <c r="L11" t="n">
-        <v>137340</v>
+        <v>158790</v>
       </c>
       <c r="M11" t="n">
-        <v>3375</v>
+        <v>7290</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10684.5</v>
+        <v>17136</v>
       </c>
       <c r="P11" t="n">
-        <v>13446</v>
+        <v>6696</v>
       </c>
       <c r="Q11" t="n">
-        <v>26491.46</v>
+        <v>259720.2</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>32670</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>9.27</v>
       </c>
       <c r="L12" t="n">
-        <v>63210</v>
+        <v>78660</v>
       </c>
       <c r="M12" t="n">
-        <v>2422.5</v>
+        <v>4845</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5910</v>
+        <v>15060</v>
       </c>
       <c r="P12" t="n">
-        <v>15420</v>
+        <v>15390</v>
       </c>
       <c r="Q12" t="n">
-        <v>17073.06</v>
+        <v>167382.9</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>32010</v>
+        <v>41490</v>
       </c>
       <c r="M13" t="n">
-        <v>2100</v>
+        <v>4620</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>4080</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>12960</v>
       </c>
       <c r="Q13" t="n">
-        <v>9615.59</v>
+        <v>94270.5</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8910</v>
+        <v>15120</v>
       </c>
       <c r="M14" t="n">
-        <v>1140</v>
+        <v>5220</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1770</v>
+        <v>2070</v>
       </c>
       <c r="P14" t="n">
-        <v>12840</v>
+        <v>12180</v>
       </c>
       <c r="Q14" t="n">
-        <v>4232.16</v>
+        <v>41491.8</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4860</v>
+        <v>9390</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>1800</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2910</v>
       </c>
       <c r="P15" t="n">
-        <v>15300</v>
+        <v>15630</v>
       </c>
       <c r="Q15" t="n">
-        <v>1299.52</v>
+        <v>12740.4</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1080</v>
+        <v>7470</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>25980</v>
+        <v>29730</v>
       </c>
       <c r="Q16" t="n">
-        <v>559.7</v>
+        <v>5487.3</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2700</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13740</v>
+        <v>18120</v>
       </c>
       <c r="Q17" t="n">
-        <v>225</v>
+        <v>2205.9</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>30</v>
       </c>
       <c r="P18" t="n">
-        <v>16440</v>
+        <v>17610</v>
       </c>
       <c r="Q18" t="n">
-        <v>123.47</v>
+        <v>1210.5</v>
       </c>
     </row>
     <row r="19">
@@ -25915,22 +25915,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>210</v>
+        <v>1470</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P19" t="n">
-        <v>17730</v>
+        <v>26010</v>
       </c>
       <c r="Q19" t="n">
-        <v>99.51000000000001</v>
+        <v>975.6</v>
       </c>
     </row>
     <row r="20">
@@ -25968,10 +25968,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6630</v>
+        <v>16530</v>
       </c>
       <c r="Q20" t="n">
-        <v>44.98</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21">
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.37</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>13296960</v>
+        <v>10773000</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -26465,22 +26465,22 @@
         <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
-        <v>6156486</v>
+        <v>5598558</v>
       </c>
       <c r="M5" t="n">
-        <v>139860</v>
+        <v>218190</v>
       </c>
       <c r="N5" t="n">
-        <v>35394</v>
+        <v>34170</v>
       </c>
       <c r="O5" t="n">
-        <v>166515</v>
+        <v>170085</v>
       </c>
       <c r="P5" t="n">
-        <v>3471</v>
+        <v>1092</v>
       </c>
       <c r="Q5" t="n">
-        <v>530971.2</v>
+        <v>5205600</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>174474</v>
       </c>
       <c r="H6" t="n">
-        <v>41814630</v>
+        <v>44251380</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
-        <v>10757232</v>
+        <v>10137852</v>
       </c>
       <c r="M6" t="n">
-        <v>248640</v>
+        <v>414120</v>
       </c>
       <c r="N6" t="n">
-        <v>133620</v>
+        <v>158355</v>
       </c>
       <c r="O6" t="n">
-        <v>852975</v>
+        <v>951150</v>
       </c>
       <c r="P6" t="n">
-        <v>28957.5</v>
+        <v>10822.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>9539057.34</v>
+        <v>93520170</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>469476</v>
       </c>
       <c r="H7" t="n">
-        <v>54051390</v>
+        <v>55674180</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1951659.86</v>
       </c>
       <c r="L7" t="n">
-        <v>19346040</v>
+        <v>19605240</v>
       </c>
       <c r="M7" t="n">
-        <v>606375</v>
+        <v>1609650</v>
       </c>
       <c r="N7" t="n">
-        <v>95676</v>
+        <v>118167</v>
       </c>
       <c r="O7" t="n">
-        <v>1178100</v>
+        <v>1156680</v>
       </c>
       <c r="P7" t="n">
-        <v>69712.5</v>
+        <v>26325</v>
       </c>
       <c r="Q7" t="n">
-        <v>10918618.56</v>
+        <v>107045280</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2813616</v>
       </c>
       <c r="H8" t="n">
-        <v>96076350</v>
+        <v>90553050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1786860.8</v>
       </c>
       <c r="L8" t="n">
-        <v>27961362</v>
+        <v>26838000</v>
       </c>
       <c r="M8" t="n">
-        <v>935550</v>
+        <v>2454375</v>
       </c>
       <c r="N8" t="n">
-        <v>82620</v>
+        <v>114240</v>
       </c>
       <c r="O8" t="n">
-        <v>1675350</v>
+        <v>1767150</v>
       </c>
       <c r="P8" t="n">
-        <v>134121</v>
+        <v>78546</v>
       </c>
       <c r="Q8" t="n">
-        <v>13176837.97</v>
+        <v>129184686</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4241160</v>
       </c>
       <c r="H9" t="n">
-        <v>40698000</v>
+        <v>49932000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -26677,22 +26677,22 @@
         <v>2339428.08</v>
       </c>
       <c r="L9" t="n">
-        <v>35809938</v>
+        <v>37126512</v>
       </c>
       <c r="M9" t="n">
-        <v>1161300</v>
+        <v>2822400</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1918620</v>
+        <v>2061675</v>
       </c>
       <c r="P9" t="n">
-        <v>280800</v>
+        <v>202800</v>
       </c>
       <c r="Q9" t="n">
-        <v>15952573.09</v>
+        <v>156397775.4</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>5660280</v>
       </c>
       <c r="H10" t="n">
-        <v>4959000</v>
+        <v>8379000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2365648.32</v>
       </c>
       <c r="L10" t="n">
-        <v>35170308</v>
+        <v>37299366</v>
       </c>
       <c r="M10" t="n">
-        <v>1526175</v>
+        <v>2606100</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2541840</v>
+        <v>2916690</v>
       </c>
       <c r="P10" t="n">
-        <v>639795</v>
+        <v>366307.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>18123468.12</v>
+        <v>177681060</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>3392280</v>
       </c>
       <c r="H11" t="n">
-        <v>2736000</v>
+        <v>3078000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1657847.51</v>
       </c>
       <c r="L11" t="n">
-        <v>24721200</v>
+        <v>28582200</v>
       </c>
       <c r="M11" t="n">
-        <v>1181250</v>
+        <v>2551500</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1816365</v>
+        <v>2913120</v>
       </c>
       <c r="P11" t="n">
-        <v>873990</v>
+        <v>435240</v>
       </c>
       <c r="Q11" t="n">
-        <v>15894876.24</v>
+        <v>155832120</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1764180</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>450114.12</v>
       </c>
       <c r="L12" t="n">
-        <v>11377800</v>
+        <v>14158800</v>
       </c>
       <c r="M12" t="n">
-        <v>847875</v>
+        <v>1695750</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1004700</v>
+        <v>2560200</v>
       </c>
       <c r="P12" t="n">
-        <v>1002300</v>
+        <v>1000350</v>
       </c>
       <c r="Q12" t="n">
-        <v>10243833.48</v>
+        <v>100429740</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>5761800</v>
+        <v>7468200</v>
       </c>
       <c r="M13" t="n">
-        <v>735000</v>
+        <v>1617000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>418200</v>
+        <v>693600</v>
       </c>
       <c r="P13" t="n">
-        <v>807300</v>
+        <v>842400</v>
       </c>
       <c r="Q13" t="n">
-        <v>5769354.6</v>
+        <v>56562300</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1603800</v>
+        <v>2721600</v>
       </c>
       <c r="M14" t="n">
-        <v>399000</v>
+        <v>1827000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>300900</v>
+        <v>351900</v>
       </c>
       <c r="P14" t="n">
-        <v>834600</v>
+        <v>791700</v>
       </c>
       <c r="Q14" t="n">
-        <v>2539298.16</v>
+        <v>24895080</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>874800</v>
+        <v>1690200</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>630000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>459000</v>
+        <v>494700</v>
       </c>
       <c r="P15" t="n">
-        <v>994500</v>
+        <v>1015950</v>
       </c>
       <c r="Q15" t="n">
-        <v>779712.48</v>
+        <v>7644240</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>194400</v>
+        <v>1344600</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>294000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>20400</v>
+        <v>86700</v>
       </c>
       <c r="P16" t="n">
-        <v>1688700</v>
+        <v>1932450</v>
       </c>
       <c r="Q16" t="n">
-        <v>335822.76</v>
+        <v>3292380</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>70200</v>
+        <v>486000</v>
       </c>
       <c r="M17" t="n">
-        <v>42000</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>893100</v>
+        <v>1177800</v>
       </c>
       <c r="Q17" t="n">
-        <v>135001.08</v>
+        <v>1323540</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16200</v>
+        <v>291600</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>105000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>5100</v>
       </c>
       <c r="P18" t="n">
-        <v>1068600</v>
+        <v>1144650</v>
       </c>
       <c r="Q18" t="n">
-        <v>74082.60000000001</v>
+        <v>726300</v>
       </c>
     </row>
     <row r="19">
@@ -27207,22 +27207,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>37800</v>
+        <v>264600</v>
       </c>
       <c r="M19" t="n">
-        <v>42000</v>
+        <v>31500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5100</v>
+        <v>15300</v>
       </c>
       <c r="P19" t="n">
-        <v>1152450</v>
+        <v>1690650</v>
       </c>
       <c r="Q19" t="n">
-        <v>59706.72</v>
+        <v>585360</v>
       </c>
     </row>
     <row r="20">
@@ -27260,10 +27260,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>430950</v>
+        <v>1074450</v>
       </c>
       <c r="Q20" t="n">
-        <v>26989.2</v>
+        <v>264600</v>
       </c>
     </row>
     <row r="21">
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>4957.2</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="22">
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>220.32</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>130290</v>
       </c>
       <c r="H4" t="n">
-        <v>16170</v>
+        <v>17910</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>405750</v>
+        <v>425160</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57090</v>
+        <v>54360</v>
       </c>
       <c r="P4" t="n">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>43492.72</v>
+        <v>605594.88</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>118260</v>
       </c>
       <c r="H5" t="n">
-        <v>22860</v>
+        <v>23130</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>284370</v>
+        <v>308340</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>56640</v>
+        <v>58590</v>
       </c>
       <c r="P5" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29817.42</v>
+        <v>415179.27</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>58890</v>
       </c>
       <c r="H6" t="n">
-        <v>15720</v>
+        <v>15210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>142680</v>
+        <v>148380</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34200</v>
+        <v>35010</v>
       </c>
       <c r="P6" t="n">
-        <v>1530</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>16454.82</v>
+        <v>229117.68</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>39360</v>
       </c>
       <c r="H7" t="n">
-        <v>17430</v>
+        <v>18240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>94800</v>
+        <v>99120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>28740</v>
+        <v>31710</v>
       </c>
       <c r="P7" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7289.95</v>
+        <v>101505.69</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>15510</v>
       </c>
       <c r="H8" t="n">
-        <v>2670</v>
+        <v>3120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>36870</v>
+        <v>41910</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11490</v>
+        <v>13290</v>
       </c>
       <c r="P8" t="n">
-        <v>3870</v>
+        <v>480</v>
       </c>
       <c r="Q8" t="n">
-        <v>3575.48</v>
+        <v>49785.12</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>480</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5850</v>
+        <v>7560</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5610</v>
+        <v>9690</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>1290</v>
       </c>
       <c r="Q9" t="n">
-        <v>183.44</v>
+        <v>2554.2</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1020</v>
+        <v>1830</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2040</v>
+        <v>7260</v>
       </c>
       <c r="P10" t="n">
-        <v>5580</v>
+        <v>5100</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.71</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>240</v>
+        <v>2490</v>
       </c>
       <c r="P11" t="n">
-        <v>5010</v>
+        <v>8910</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.43</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28137,13 +28137,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2550</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1410</v>
+        <v>4920</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -28287,7 +28287,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -28299,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8229.6</v>
+        <v>8326.799999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>17.87</v>
       </c>
       <c r="L5" t="n">
-        <v>59717.7</v>
+        <v>64751.4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2832</v>
+        <v>2929.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1490.87</v>
+        <v>20758.96</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2944.5</v>
       </c>
       <c r="H6" t="n">
-        <v>8960.4</v>
+        <v>8669.700000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>18.25</v>
       </c>
       <c r="L6" t="n">
-        <v>52791.6</v>
+        <v>54900.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8550</v>
+        <v>8752.5</v>
       </c>
       <c r="P6" t="n">
-        <v>229.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12341.11</v>
+        <v>171838.26</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>5904</v>
       </c>
       <c r="H7" t="n">
-        <v>12723.9</v>
+        <v>13315.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>10.85</v>
       </c>
       <c r="L7" t="n">
-        <v>56880</v>
+        <v>59472</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10059</v>
+        <v>11098.5</v>
       </c>
       <c r="P7" t="n">
-        <v>577.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5831.96</v>
+        <v>81204.55</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>10081.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2269.5</v>
+        <v>2652</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>26177.7</v>
+        <v>29756.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5170.5</v>
+        <v>5980.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1470.6</v>
+        <v>182.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3396.7</v>
+        <v>47295.86</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>408</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4738.5</v>
+        <v>6123.6</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3085.5</v>
+        <v>5329.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2160</v>
+        <v>645</v>
       </c>
       <c r="Q9" t="n">
-        <v>177.93</v>
+        <v>2477.57</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>907.8</v>
+        <v>1628.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1428</v>
+        <v>5082</v>
       </c>
       <c r="P10" t="n">
-        <v>4743</v>
+        <v>4335</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.71</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>204</v>
+        <v>2116.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4509</v>
+        <v>8019</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.43</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29429,13 +29429,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2550</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1410</v>
+        <v>4920</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -29579,7 +29579,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -29591,7 +29591,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46908720</v>
+        <v>47462760</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
-        <v>10749186</v>
+        <v>11655252</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>481440</v>
+        <v>498015</v>
       </c>
       <c r="P5" t="n">
-        <v>702</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>894522.61</v>
+        <v>12455378.1</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>159003</v>
       </c>
       <c r="H6" t="n">
-        <v>51074280</v>
+        <v>49417290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>886244.11</v>
       </c>
       <c r="L6" t="n">
-        <v>9502488</v>
+        <v>9882108</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1453500</v>
+        <v>1487925</v>
       </c>
       <c r="P6" t="n">
-        <v>14917.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7404666.84</v>
+        <v>103102956</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>318816</v>
       </c>
       <c r="H7" t="n">
-        <v>72526230</v>
+        <v>75896640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>526638.38</v>
       </c>
       <c r="L7" t="n">
-        <v>10238400</v>
+        <v>10704960</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1710030</v>
+        <v>1886745</v>
       </c>
       <c r="P7" t="n">
-        <v>37537.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3499177.97</v>
+        <v>48722731.2</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>544401</v>
       </c>
       <c r="H8" t="n">
-        <v>12936150</v>
+        <v>15116400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>4711986</v>
+        <v>5356098</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>878985</v>
+        <v>1016685</v>
       </c>
       <c r="P8" t="n">
-        <v>95589</v>
+        <v>11856</v>
       </c>
       <c r="Q8" t="n">
-        <v>2038021.78</v>
+        <v>28377518.4</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>22032</v>
       </c>
       <c r="H9" t="n">
-        <v>2394000</v>
+        <v>3078000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>852930</v>
+        <v>1102248</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>524535</v>
+        <v>906015</v>
       </c>
       <c r="P9" t="n">
-        <v>140400</v>
+        <v>41925</v>
       </c>
       <c r="Q9" t="n">
-        <v>106760.92</v>
+        <v>1486544.4</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>8100</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>163404</v>
+        <v>293166</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>242760</v>
+        <v>863940</v>
       </c>
       <c r="P10" t="n">
-        <v>308295</v>
+        <v>281775</v>
       </c>
       <c r="Q10" t="n">
-        <v>19623.6</v>
+        <v>273240</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>70200</v>
+        <v>459000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>34680</v>
+        <v>359805</v>
       </c>
       <c r="P11" t="n">
-        <v>293085</v>
+        <v>521235</v>
       </c>
       <c r="Q11" t="n">
-        <v>9257.219999999999</v>
+        <v>128898</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1710000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16200</v>
+        <v>291600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30721,13 +30721,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P12" t="n">
-        <v>165750</v>
+        <v>405600</v>
       </c>
       <c r="Q12" t="n">
-        <v>2218.32</v>
+        <v>30888</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>91650</v>
+        <v>319800</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.64</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11700</v>
+        <v>66300</v>
       </c>
       <c r="Q14" t="n">
-        <v>85.31999999999999</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15">
@@ -30871,7 +30871,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -30883,7 +30883,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
